--- a/sample_two_years.xlsx
+++ b/sample_two_years.xlsx
@@ -7,12 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2024-25 logbook" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-26 logbook" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2025-26 logbook" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-27 logbook" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2024-25 logbook'!$26:$26</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2025-26 logbook'!$26:$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'2025-26 logbook'!$26:$26</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'2026-27 logbook'!$26:$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -532,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -583,7 +583,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Yash Vadukiya</t>
+          <t>Sam Taylor</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Corolla Hybrid</t>
+          <t>Corolla</t>
         </is>
       </c>
     </row>
@@ -643,7 +643,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>ABC123</t>
+          <t>XYZ789</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>45778</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="14">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>45838</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="15">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="16">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>25954</v>
+        <v>37185</v>
       </c>
     </row>
     <row r="17">
@@ -735,7 +735,7 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>8000</v>
+        <v>10400</v>
       </c>
     </row>
     <row r="21">
@@ -745,7 +745,7 @@
         </is>
       </c>
       <c r="D21" s="8">
-        <f>I90</f>
+        <f>I88</f>
         <v/>
       </c>
     </row>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="D22" s="8">
-        <f>I91</f>
+        <f>I89</f>
         <v/>
       </c>
     </row>
@@ -834,10 +834,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="14" t="n">
-        <v>45779</v>
+        <v>46143</v>
       </c>
       <c r="C27" s="14" t="n">
-        <v>45779</v>
+        <v>46143</v>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
@@ -846,19 +846,19 @@
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Food delivery run</t>
+          <t>Rideshare fares - suburban runs</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>Aspley / Nundah</t>
+          <t>Sydney Airport / Parramatta</t>
         </is>
       </c>
       <c r="G27" s="16" t="n">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>20220</v>
+        <v>30269</v>
       </c>
       <c r="I27" s="16">
         <f>H27-G27</f>
@@ -870,10 +870,10 @@
         <v>2</v>
       </c>
       <c r="B28" s="14" t="n">
-        <v>45779</v>
+        <v>46143</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>45779</v>
+        <v>46143</v>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
       </c>
       <c r="F28" s="15" t="inlineStr"/>
       <c r="G28" s="16" t="n">
-        <v>20220</v>
+        <v>30269</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>20274</v>
+        <v>30327</v>
       </c>
       <c r="I28" s="16">
         <f>H28-G28</f>
@@ -902,31 +902,27 @@
         <v>3</v>
       </c>
       <c r="B29" s="14" t="n">
-        <v>45781</v>
+        <v>46144</v>
       </c>
       <c r="C29" s="14" t="n">
-        <v>45781</v>
+        <v>46144</v>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - event and venue pickups</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
-        <is>
-          <t>West End / Hamilton</t>
-        </is>
-      </c>
+          <t>Private use - family travel</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr"/>
       <c r="G29" s="16" t="n">
-        <v>20274</v>
+        <v>30327</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>20535</v>
+        <v>30365</v>
       </c>
       <c r="I29" s="16">
         <f>H29-G29</f>
@@ -938,27 +934,31 @@
         <v>4</v>
       </c>
       <c r="B30" s="14" t="n">
-        <v>45781</v>
+        <v>46145</v>
       </c>
       <c r="C30" s="14" t="n">
-        <v>45781</v>
+        <v>46145</v>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr"/>
+          <t>Rideshare fares - late night runs</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>Castle Hill / Newtown</t>
+        </is>
+      </c>
       <c r="G30" s="16" t="n">
-        <v>20535</v>
+        <v>30365</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>20566</v>
+        <v>30683</v>
       </c>
       <c r="I30" s="16">
         <f>H30-G30</f>
@@ -970,10 +970,10 @@
         <v>5</v>
       </c>
       <c r="B31" s="14" t="n">
-        <v>45782</v>
+        <v>46146</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>45782</v>
+        <v>46146</v>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
@@ -982,15 +982,15 @@
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal travel</t>
+          <t>Private use - personal errands</t>
         </is>
       </c>
       <c r="F31" s="15" t="inlineStr"/>
       <c r="G31" s="16" t="n">
-        <v>20566</v>
+        <v>30683</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>20622</v>
+        <v>30723</v>
       </c>
       <c r="I31" s="16">
         <f>H31-G31</f>
@@ -1002,10 +1002,10 @@
         <v>6</v>
       </c>
       <c r="B32" s="14" t="n">
-        <v>45783</v>
+        <v>46147</v>
       </c>
       <c r="C32" s="14" t="n">
-        <v>45783</v>
+        <v>46147</v>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
@@ -1014,15 +1014,15 @@
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
+          <t>Private use - weekend outing</t>
         </is>
       </c>
       <c r="F32" s="15" t="inlineStr"/>
       <c r="G32" s="16" t="n">
-        <v>20622</v>
+        <v>30723</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>20672</v>
+        <v>30792</v>
       </c>
       <c r="I32" s="16">
         <f>H32-G32</f>
@@ -1034,27 +1034,31 @@
         <v>7</v>
       </c>
       <c r="B33" s="14" t="n">
-        <v>45785</v>
+        <v>46150</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>45785</v>
+        <v>46150</v>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr"/>
+          <t>Rideshare fares - evening shift</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Sydney Airport</t>
+        </is>
+      </c>
       <c r="G33" s="16" t="n">
-        <v>20672</v>
+        <v>30792</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>20702</v>
+        <v>30931</v>
       </c>
       <c r="I33" s="16">
         <f>H33-G33</f>
@@ -1066,31 +1070,27 @@
         <v>8</v>
       </c>
       <c r="B34" s="14" t="n">
-        <v>45786</v>
+        <v>46150</v>
       </c>
       <c r="C34" s="14" t="n">
-        <v>45786</v>
+        <v>46150</v>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Multi-drop delivery round</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>Sunnybank</t>
-        </is>
-      </c>
+          <t>Private use - visiting friends</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr"/>
       <c r="G34" s="16" t="n">
-        <v>20702</v>
+        <v>30931</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>20815</v>
+        <v>30971</v>
       </c>
       <c r="I34" s="16">
         <f>H34-G34</f>
@@ -1102,27 +1102,31 @@
         <v>9</v>
       </c>
       <c r="B35" s="14" t="n">
-        <v>45786</v>
+        <v>46151</v>
       </c>
       <c r="C35" s="14" t="n">
-        <v>45786</v>
+        <v>46151</v>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr"/>
+          <t>Rideshare fares - passenger trips</t>
+        </is>
+      </c>
+      <c r="F35" s="15" t="inlineStr">
+        <is>
+          <t>Randwick / Marrickville</t>
+        </is>
+      </c>
       <c r="G35" s="16" t="n">
-        <v>20815</v>
+        <v>30971</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>20842</v>
+        <v>31288</v>
       </c>
       <c r="I35" s="16">
         <f>H35-G35</f>
@@ -1134,10 +1138,10 @@
         <v>10</v>
       </c>
       <c r="B36" s="14" t="n">
-        <v>45787</v>
+        <v>46152</v>
       </c>
       <c r="C36" s="14" t="n">
-        <v>45787</v>
+        <v>46152</v>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
@@ -1146,19 +1150,19 @@
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - passenger trips</t>
+          <t>Rideshare fares - late night runs</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
-          <t>Logan Central / Chermside</t>
+          <t>Parramatta / Randwick</t>
         </is>
       </c>
       <c r="G36" s="16" t="n">
-        <v>20842</v>
+        <v>31288</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>21102</v>
+        <v>31581</v>
       </c>
       <c r="I36" s="16">
         <f>H36-G36</f>
@@ -1170,10 +1174,10 @@
         <v>11</v>
       </c>
       <c r="B37" s="14" t="n">
-        <v>45787</v>
+        <v>46152</v>
       </c>
       <c r="C37" s="14" t="n">
-        <v>45787</v>
+        <v>46152</v>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
@@ -1182,15 +1186,15 @@
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal travel</t>
+          <t>Private use - personal errands</t>
         </is>
       </c>
       <c r="F37" s="15" t="inlineStr"/>
       <c r="G37" s="16" t="n">
-        <v>21102</v>
+        <v>31581</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>21142</v>
+        <v>31627</v>
       </c>
       <c r="I37" s="16">
         <f>H37-G37</f>
@@ -1202,31 +1206,27 @@
         <v>12</v>
       </c>
       <c r="B38" s="14" t="n">
-        <v>45788</v>
+        <v>46153</v>
       </c>
       <c r="C38" s="14" t="n">
-        <v>45788</v>
+        <v>46153</v>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Grocery delivery run</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr">
-        <is>
-          <t>Nundah / North Lakes</t>
-        </is>
-      </c>
+          <t>Private use - visiting friends</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr"/>
       <c r="G38" s="16" t="n">
-        <v>21142</v>
+        <v>31627</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>21382</v>
+        <v>31679</v>
       </c>
       <c r="I38" s="16">
         <f>H38-G38</f>
@@ -1238,10 +1238,10 @@
         <v>13</v>
       </c>
       <c r="B39" s="14" t="n">
-        <v>45788</v>
+        <v>46154</v>
       </c>
       <c r="C39" s="14" t="n">
-        <v>45788</v>
+        <v>46154</v>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
@@ -1250,15 +1250,15 @@
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal travel</t>
+          <t>Private use - visiting friends</t>
         </is>
       </c>
       <c r="F39" s="15" t="inlineStr"/>
       <c r="G39" s="16" t="n">
-        <v>21382</v>
+        <v>31679</v>
       </c>
       <c r="H39" s="16" t="n">
-        <v>21421</v>
+        <v>31723</v>
       </c>
       <c r="I39" s="16">
         <f>H39-G39</f>
@@ -1270,10 +1270,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="14" t="n">
-        <v>45789</v>
+        <v>46155</v>
       </c>
       <c r="C40" s="14" t="n">
-        <v>45789</v>
+        <v>46155</v>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
@@ -1282,15 +1282,15 @@
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal travel</t>
+          <t>Private use - weekend outing</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr"/>
       <c r="G40" s="16" t="n">
-        <v>21421</v>
+        <v>31723</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>21454</v>
+        <v>31791</v>
       </c>
       <c r="I40" s="16">
         <f>H40-G40</f>
@@ -1302,10 +1302,10 @@
         <v>15</v>
       </c>
       <c r="B41" s="14" t="n">
-        <v>45790</v>
+        <v>46156</v>
       </c>
       <c r="C41" s="14" t="n">
-        <v>45790</v>
+        <v>46156</v>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
@@ -1314,15 +1314,15 @@
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
+          <t>Private use - family travel</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr"/>
       <c r="G41" s="16" t="n">
-        <v>21454</v>
+        <v>31791</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>21526</v>
+        <v>31832</v>
       </c>
       <c r="I41" s="16">
         <f>H41-G41</f>
@@ -1334,27 +1334,31 @@
         <v>16</v>
       </c>
       <c r="B42" s="14" t="n">
-        <v>45791</v>
+        <v>46157</v>
       </c>
       <c r="C42" s="14" t="n">
-        <v>45791</v>
+        <v>46157</v>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="inlineStr"/>
+          <t>Rideshare fares - weekend shift</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>Pyrmont</t>
+        </is>
+      </c>
       <c r="G42" s="16" t="n">
-        <v>21526</v>
+        <v>31832</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>21599</v>
+        <v>32045</v>
       </c>
       <c r="I42" s="16">
         <f>H42-G42</f>
@@ -1366,10 +1370,10 @@
         <v>17</v>
       </c>
       <c r="B43" s="14" t="n">
-        <v>45792</v>
+        <v>46157</v>
       </c>
       <c r="C43" s="14" t="n">
-        <v>45792</v>
+        <v>46157</v>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
@@ -1378,15 +1382,15 @@
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
+          <t>Private use - personal errands</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr"/>
       <c r="G43" s="16" t="n">
-        <v>21599</v>
+        <v>32045</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>21655</v>
+        <v>32119</v>
       </c>
       <c r="I43" s="16">
         <f>H43-G43</f>
@@ -1398,31 +1402,27 @@
         <v>18</v>
       </c>
       <c r="B44" s="14" t="n">
-        <v>45793</v>
+        <v>46158</v>
       </c>
       <c r="C44" s="14" t="n">
-        <v>45793</v>
+        <v>46158</v>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - suburban runs</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="inlineStr">
-        <is>
-          <t>Chermside</t>
-        </is>
-      </c>
+          <t>Private use - weekend outing</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr"/>
       <c r="G44" s="16" t="n">
-        <v>21655</v>
+        <v>32119</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>21829</v>
+        <v>32153</v>
       </c>
       <c r="I44" s="16">
         <f>H44-G44</f>
@@ -1434,27 +1434,31 @@
         <v>19</v>
       </c>
       <c r="B45" s="14" t="n">
-        <v>45794</v>
+        <v>46159</v>
       </c>
       <c r="C45" s="14" t="n">
-        <v>45794</v>
+        <v>46159</v>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
-        </is>
-      </c>
-      <c r="F45" s="15" t="inlineStr"/>
+          <t>Rideshare fares - weekend shift</t>
+        </is>
+      </c>
+      <c r="F45" s="15" t="inlineStr">
+        <is>
+          <t>Bondi</t>
+        </is>
+      </c>
       <c r="G45" s="16" t="n">
-        <v>21829</v>
+        <v>32153</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>21870</v>
+        <v>32325</v>
       </c>
       <c r="I45" s="16">
         <f>H45-G45</f>
@@ -1466,31 +1470,27 @@
         <v>20</v>
       </c>
       <c r="B46" s="14" t="n">
-        <v>45795</v>
+        <v>46159</v>
       </c>
       <c r="C46" s="14" t="n">
-        <v>45795</v>
+        <v>46159</v>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Food delivery - dinner peak</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr">
-        <is>
-          <t>Mount Gravatt</t>
-        </is>
-      </c>
+          <t>Private use - weekend outing</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr"/>
       <c r="G46" s="16" t="n">
-        <v>21870</v>
+        <v>32325</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>22011</v>
+        <v>32396</v>
       </c>
       <c r="I46" s="16">
         <f>H46-G46</f>
@@ -1502,10 +1502,10 @@
         <v>21</v>
       </c>
       <c r="B47" s="14" t="n">
-        <v>45796</v>
+        <v>46160</v>
       </c>
       <c r="C47" s="14" t="n">
-        <v>45796</v>
+        <v>46160</v>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
@@ -1514,15 +1514,15 @@
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F47" s="15" t="inlineStr"/>
       <c r="G47" s="16" t="n">
-        <v>22011</v>
+        <v>32396</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>22081</v>
+        <v>32427</v>
       </c>
       <c r="I47" s="16">
         <f>H47-G47</f>
@@ -1534,10 +1534,10 @@
         <v>22</v>
       </c>
       <c r="B48" s="14" t="n">
-        <v>45797</v>
+        <v>46163</v>
       </c>
       <c r="C48" s="14" t="n">
-        <v>45797</v>
+        <v>46163</v>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
@@ -1546,15 +1546,15 @@
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
+          <t>Private use - weekend outing</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr"/>
       <c r="G48" s="16" t="n">
-        <v>22081</v>
+        <v>32427</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>22139</v>
+        <v>32466</v>
       </c>
       <c r="I48" s="16">
         <f>H48-G48</f>
@@ -1566,10 +1566,10 @@
         <v>23</v>
       </c>
       <c r="B49" s="14" t="n">
-        <v>45800</v>
+        <v>46164</v>
       </c>
       <c r="C49" s="14" t="n">
-        <v>45800</v>
+        <v>46164</v>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
@@ -1578,15 +1578,15 @@
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>Private use - shopping trip</t>
+          <t>Private use - personal travel</t>
         </is>
       </c>
       <c r="F49" s="15" t="inlineStr"/>
       <c r="G49" s="16" t="n">
-        <v>22139</v>
+        <v>32466</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>22190</v>
+        <v>32540</v>
       </c>
       <c r="I49" s="16">
         <f>H49-G49</f>
@@ -1598,10 +1598,10 @@
         <v>24</v>
       </c>
       <c r="B50" s="14" t="n">
-        <v>45801</v>
+        <v>46165</v>
       </c>
       <c r="C50" s="14" t="n">
-        <v>45801</v>
+        <v>46165</v>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
@@ -1610,19 +1610,19 @@
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - suburban runs</t>
+          <t>Rideshare fares - event and venue pickups</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>Newstead / Brisbane CBD</t>
+          <t>Parramatta / Castle Hill</t>
         </is>
       </c>
       <c r="G50" s="16" t="n">
-        <v>22190</v>
+        <v>32540</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>22478</v>
+        <v>32890</v>
       </c>
       <c r="I50" s="16">
         <f>H50-G50</f>
@@ -1634,27 +1634,31 @@
         <v>25</v>
       </c>
       <c r="B51" s="14" t="n">
-        <v>45801</v>
+        <v>46166</v>
       </c>
       <c r="C51" s="14" t="n">
-        <v>45801</v>
+        <v>46166</v>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal travel</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="inlineStr"/>
+          <t>Rideshare fares - late night runs</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>Surry Hills</t>
+        </is>
+      </c>
       <c r="G51" s="16" t="n">
-        <v>22478</v>
+        <v>32890</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>22521</v>
+        <v>33102</v>
       </c>
       <c r="I51" s="16">
         <f>H51-G51</f>
@@ -1666,31 +1670,27 @@
         <v>26</v>
       </c>
       <c r="B52" s="14" t="n">
-        <v>45802</v>
+        <v>46166</v>
       </c>
       <c r="C52" s="14" t="n">
-        <v>45802</v>
+        <v>46166</v>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Parcel delivery run</t>
-        </is>
-      </c>
-      <c r="F52" s="15" t="inlineStr">
-        <is>
-          <t>Toowong</t>
-        </is>
-      </c>
+          <t>Private use - weekend outing</t>
+        </is>
+      </c>
+      <c r="F52" s="15" t="inlineStr"/>
       <c r="G52" s="16" t="n">
-        <v>22521</v>
+        <v>33102</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>22695</v>
+        <v>33138</v>
       </c>
       <c r="I52" s="16">
         <f>H52-G52</f>
@@ -1702,10 +1702,10 @@
         <v>27</v>
       </c>
       <c r="B53" s="14" t="n">
-        <v>45803</v>
+        <v>46167</v>
       </c>
       <c r="C53" s="14" t="n">
-        <v>45803</v>
+        <v>46167</v>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
       </c>
       <c r="F53" s="15" t="inlineStr"/>
       <c r="G53" s="16" t="n">
-        <v>22695</v>
+        <v>33138</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>22732</v>
+        <v>33183</v>
       </c>
       <c r="I53" s="16">
         <f>H53-G53</f>
@@ -1734,10 +1734,10 @@
         <v>28</v>
       </c>
       <c r="B54" s="14" t="n">
-        <v>45804</v>
+        <v>46170</v>
       </c>
       <c r="C54" s="14" t="n">
-        <v>45804</v>
+        <v>46170</v>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
@@ -1746,15 +1746,15 @@
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr"/>
       <c r="G54" s="16" t="n">
-        <v>22732</v>
+        <v>33183</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>22768</v>
+        <v>33254</v>
       </c>
       <c r="I54" s="16">
         <f>H54-G54</f>
@@ -1766,10 +1766,10 @@
         <v>29</v>
       </c>
       <c r="B55" s="14" t="n">
-        <v>45805</v>
+        <v>46171</v>
       </c>
       <c r="C55" s="14" t="n">
-        <v>45805</v>
+        <v>46171</v>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
@@ -1778,15 +1778,15 @@
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal travel</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F55" s="15" t="inlineStr"/>
       <c r="G55" s="16" t="n">
-        <v>22768</v>
+        <v>33254</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>22813</v>
+        <v>33317</v>
       </c>
       <c r="I55" s="16">
         <f>H55-G55</f>
@@ -1798,27 +1798,31 @@
         <v>30</v>
       </c>
       <c r="B56" s="14" t="n">
-        <v>45806</v>
+        <v>46172</v>
       </c>
       <c r="C56" s="14" t="n">
-        <v>45806</v>
+        <v>46172</v>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
-        </is>
-      </c>
-      <c r="F56" s="15" t="inlineStr"/>
+          <t>Rideshare fares - passenger trips</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>Bondi</t>
+        </is>
+      </c>
       <c r="G56" s="16" t="n">
-        <v>22813</v>
+        <v>33317</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>22886</v>
+        <v>33475</v>
       </c>
       <c r="I56" s="16">
         <f>H56-G56</f>
@@ -1830,10 +1834,10 @@
         <v>31</v>
       </c>
       <c r="B57" s="14" t="n">
-        <v>45807</v>
+        <v>46172</v>
       </c>
       <c r="C57" s="14" t="n">
-        <v>45807</v>
+        <v>46172</v>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
@@ -1842,15 +1846,15 @@
       </c>
       <c r="E57" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
+          <t>Private use - personal travel</t>
         </is>
       </c>
       <c r="F57" s="15" t="inlineStr"/>
       <c r="G57" s="16" t="n">
-        <v>22886</v>
+        <v>33475</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>22947</v>
+        <v>33533</v>
       </c>
       <c r="I57" s="16">
         <f>H57-G57</f>
@@ -1862,10 +1866,10 @@
         <v>32</v>
       </c>
       <c r="B58" s="14" t="n">
-        <v>45808</v>
+        <v>46173</v>
       </c>
       <c r="C58" s="14" t="n">
-        <v>45808</v>
+        <v>46173</v>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
@@ -1874,19 +1878,19 @@
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Courier pickups and drop-offs</t>
+          <t>Rideshare fares - weekend shift</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>Carindale</t>
+          <t>Randwick</t>
         </is>
       </c>
       <c r="G58" s="16" t="n">
-        <v>22947</v>
+        <v>33533</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>23076</v>
+        <v>33692</v>
       </c>
       <c r="I58" s="16">
         <f>H58-G58</f>
@@ -1898,10 +1902,10 @@
         <v>33</v>
       </c>
       <c r="B59" s="14" t="n">
-        <v>45808</v>
+        <v>46177</v>
       </c>
       <c r="C59" s="14" t="n">
-        <v>45808</v>
+        <v>46177</v>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
@@ -1910,15 +1914,15 @@
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
+          <t>Private use - visiting friends</t>
         </is>
       </c>
       <c r="F59" s="15" t="inlineStr"/>
       <c r="G59" s="16" t="n">
-        <v>23076</v>
+        <v>33692</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>23103</v>
+        <v>33768</v>
       </c>
       <c r="I59" s="16">
         <f>H59-G59</f>
@@ -1930,27 +1934,31 @@
         <v>34</v>
       </c>
       <c r="B60" s="14" t="n">
-        <v>45811</v>
+        <v>46178</v>
       </c>
       <c r="C60" s="14" t="n">
-        <v>45811</v>
+        <v>46178</v>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal travel</t>
-        </is>
-      </c>
-      <c r="F60" s="15" t="inlineStr"/>
+          <t>Rideshare fares - suburban runs</t>
+        </is>
+      </c>
+      <c r="F60" s="15" t="inlineStr">
+        <is>
+          <t>Surry Hills / Pyrmont</t>
+        </is>
+      </c>
       <c r="G60" s="16" t="n">
-        <v>23103</v>
+        <v>33768</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>23171</v>
+        <v>34083</v>
       </c>
       <c r="I60" s="16">
         <f>H60-G60</f>
@@ -1962,27 +1970,31 @@
         <v>35</v>
       </c>
       <c r="B61" s="14" t="n">
-        <v>45812</v>
+        <v>46179</v>
       </c>
       <c r="C61" s="14" t="n">
-        <v>45812</v>
+        <v>46179</v>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E61" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
-        </is>
-      </c>
-      <c r="F61" s="15" t="inlineStr"/>
+          <t>Rideshare fares - suburban runs</t>
+        </is>
+      </c>
+      <c r="F61" s="15" t="inlineStr">
+        <is>
+          <t>Randwick</t>
+        </is>
+      </c>
       <c r="G61" s="16" t="n">
-        <v>23171</v>
+        <v>34083</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>23242</v>
+        <v>34240</v>
       </c>
       <c r="I61" s="16">
         <f>H61-G61</f>
@@ -1994,10 +2006,10 @@
         <v>36</v>
       </c>
       <c r="B62" s="14" t="n">
-        <v>45813</v>
+        <v>46179</v>
       </c>
       <c r="C62" s="14" t="n">
-        <v>45813</v>
+        <v>46179</v>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
@@ -2006,15 +2018,15 @@
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
+          <t>Private use - personal errands</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr"/>
       <c r="G62" s="16" t="n">
-        <v>23242</v>
+        <v>34240</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>23315</v>
+        <v>34271</v>
       </c>
       <c r="I62" s="16">
         <f>H62-G62</f>
@@ -2026,10 +2038,10 @@
         <v>37</v>
       </c>
       <c r="B63" s="14" t="n">
-        <v>45814</v>
+        <v>46180</v>
       </c>
       <c r="C63" s="14" t="n">
-        <v>45814</v>
+        <v>46180</v>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
@@ -2038,19 +2050,19 @@
       </c>
       <c r="E63" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - suburban runs</t>
+          <t>Rideshare fares - late night runs</t>
         </is>
       </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>Logan Central / Newstead</t>
+          <t>Marrickville</t>
         </is>
       </c>
       <c r="G63" s="16" t="n">
-        <v>23315</v>
+        <v>34271</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>23557</v>
+        <v>34472</v>
       </c>
       <c r="I63" s="16">
         <f>H63-G63</f>
@@ -2062,10 +2074,10 @@
         <v>38</v>
       </c>
       <c r="B64" s="14" t="n">
-        <v>45814</v>
+        <v>46181</v>
       </c>
       <c r="C64" s="14" t="n">
-        <v>45814</v>
+        <v>46181</v>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
@@ -2074,15 +2086,15 @@
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr"/>
       <c r="G64" s="16" t="n">
-        <v>23557</v>
+        <v>34472</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v>23596</v>
+        <v>34515</v>
       </c>
       <c r="I64" s="16">
         <f>H64-G64</f>
@@ -2094,31 +2106,27 @@
         <v>39</v>
       </c>
       <c r="B65" s="14" t="n">
-        <v>45815</v>
+        <v>46182</v>
       </c>
       <c r="C65" s="14" t="n">
-        <v>45815</v>
+        <v>46182</v>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>Grocery delivery run</t>
-        </is>
-      </c>
-      <c r="F65" s="15" t="inlineStr">
-        <is>
-          <t>Everton Park</t>
-        </is>
-      </c>
+          <t>Private use - weekend outing</t>
+        </is>
+      </c>
+      <c r="F65" s="15" t="inlineStr"/>
       <c r="G65" s="16" t="n">
-        <v>23596</v>
+        <v>34515</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>23717</v>
+        <v>34576</v>
       </c>
       <c r="I65" s="16">
         <f>H65-G65</f>
@@ -2130,10 +2138,10 @@
         <v>40</v>
       </c>
       <c r="B66" s="14" t="n">
-        <v>45815</v>
+        <v>46183</v>
       </c>
       <c r="C66" s="14" t="n">
-        <v>45815</v>
+        <v>46183</v>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
@@ -2142,15 +2150,15 @@
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
+          <t>Private use - weekend outing</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr"/>
       <c r="G66" s="16" t="n">
-        <v>23717</v>
+        <v>34576</v>
       </c>
       <c r="H66" s="16" t="n">
-        <v>23753</v>
+        <v>34625</v>
       </c>
       <c r="I66" s="16">
         <f>H66-G66</f>
@@ -2162,10 +2170,10 @@
         <v>41</v>
       </c>
       <c r="B67" s="14" t="n">
-        <v>45816</v>
+        <v>46185</v>
       </c>
       <c r="C67" s="14" t="n">
-        <v>45816</v>
+        <v>46185</v>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
@@ -2174,19 +2182,19 @@
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>Parcel delivery run</t>
+          <t>Rideshare fares - morning peak</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>North Lakes</t>
+          <t>Sydney CBD</t>
         </is>
       </c>
       <c r="G67" s="16" t="n">
-        <v>23753</v>
+        <v>34625</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>23907</v>
+        <v>34840</v>
       </c>
       <c r="I67" s="16">
         <f>H67-G67</f>
@@ -2198,10 +2206,10 @@
         <v>42</v>
       </c>
       <c r="B68" s="14" t="n">
-        <v>45816</v>
+        <v>46185</v>
       </c>
       <c r="C68" s="14" t="n">
-        <v>45816</v>
+        <v>46185</v>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
@@ -2215,10 +2223,10 @@
       </c>
       <c r="F68" s="15" t="inlineStr"/>
       <c r="G68" s="16" t="n">
-        <v>23907</v>
+        <v>34840</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>23963</v>
+        <v>34875</v>
       </c>
       <c r="I68" s="16">
         <f>H68-G68</f>
@@ -2230,27 +2238,31 @@
         <v>43</v>
       </c>
       <c r="B69" s="14" t="n">
-        <v>45818</v>
+        <v>46186</v>
       </c>
       <c r="C69" s="14" t="n">
-        <v>45818</v>
+        <v>46186</v>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="inlineStr"/>
+          <t>Rideshare fares - evening shift</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="inlineStr">
+        <is>
+          <t>Randwick</t>
+        </is>
+      </c>
       <c r="G69" s="16" t="n">
-        <v>23963</v>
+        <v>34875</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>24003</v>
+        <v>35040</v>
       </c>
       <c r="I69" s="16">
         <f>H69-G69</f>
@@ -2262,31 +2274,27 @@
         <v>44</v>
       </c>
       <c r="B70" s="14" t="n">
-        <v>45821</v>
+        <v>46186</v>
       </c>
       <c r="C70" s="14" t="n">
-        <v>45821</v>
+        <v>46186</v>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - evening shift</t>
-        </is>
-      </c>
-      <c r="F70" s="15" t="inlineStr">
-        <is>
-          <t>Brisbane Airport</t>
-        </is>
-      </c>
+          <t>Private use - weekend outing</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="inlineStr"/>
       <c r="G70" s="16" t="n">
-        <v>24003</v>
+        <v>35040</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>24169</v>
+        <v>35108</v>
       </c>
       <c r="I70" s="16">
         <f>H70-G70</f>
@@ -2298,27 +2306,31 @@
         <v>45</v>
       </c>
       <c r="B71" s="14" t="n">
-        <v>45821</v>
+        <v>46187</v>
       </c>
       <c r="C71" s="14" t="n">
-        <v>45821</v>
+        <v>46187</v>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
-        </is>
-      </c>
-      <c r="F71" s="15" t="inlineStr"/>
+          <t>Rideshare fares - weekend shift</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>Castle Hill</t>
+        </is>
+      </c>
       <c r="G71" s="16" t="n">
-        <v>24169</v>
+        <v>35108</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>24202</v>
+        <v>35310</v>
       </c>
       <c r="I71" s="16">
         <f>H71-G71</f>
@@ -2330,31 +2342,27 @@
         <v>46</v>
       </c>
       <c r="B72" s="14" t="n">
-        <v>45822</v>
+        <v>46187</v>
       </c>
       <c r="C72" s="14" t="n">
-        <v>45822</v>
+        <v>46187</v>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Grocery delivery run</t>
-        </is>
-      </c>
-      <c r="F72" s="15" t="inlineStr">
-        <is>
-          <t>Carindale</t>
-        </is>
-      </c>
+          <t>Private use - personal travel</t>
+        </is>
+      </c>
+      <c r="F72" s="15" t="inlineStr"/>
       <c r="G72" s="16" t="n">
-        <v>24202</v>
+        <v>35310</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>24329</v>
+        <v>35352</v>
       </c>
       <c r="I72" s="16">
         <f>H72-G72</f>
@@ -2366,31 +2374,27 @@
         <v>47</v>
       </c>
       <c r="B73" s="14" t="n">
-        <v>45823</v>
+        <v>46188</v>
       </c>
       <c r="C73" s="14" t="n">
-        <v>45823</v>
+        <v>46188</v>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - passenger trips</t>
-        </is>
-      </c>
-      <c r="F73" s="15" t="inlineStr">
-        <is>
-          <t>Hamilton</t>
-        </is>
-      </c>
+          <t>Private use - visiting friends</t>
+        </is>
+      </c>
+      <c r="F73" s="15" t="inlineStr"/>
       <c r="G73" s="16" t="n">
-        <v>24329</v>
+        <v>35352</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>24484</v>
+        <v>35429</v>
       </c>
       <c r="I73" s="16">
         <f>H73-G73</f>
@@ -2402,10 +2406,10 @@
         <v>48</v>
       </c>
       <c r="B74" s="14" t="n">
-        <v>45824</v>
+        <v>46189</v>
       </c>
       <c r="C74" s="14" t="n">
-        <v>45824</v>
+        <v>46189</v>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
@@ -2414,15 +2418,15 @@
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr"/>
       <c r="G74" s="16" t="n">
-        <v>24484</v>
+        <v>35429</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>24526</v>
+        <v>35484</v>
       </c>
       <c r="I74" s="16">
         <f>H74-G74</f>
@@ -2434,10 +2438,10 @@
         <v>49</v>
       </c>
       <c r="B75" s="14" t="n">
-        <v>45825</v>
+        <v>46191</v>
       </c>
       <c r="C75" s="14" t="n">
-        <v>45825</v>
+        <v>46191</v>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
@@ -2446,15 +2450,15 @@
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
+          <t>Private use - personal travel</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr"/>
       <c r="G75" s="16" t="n">
-        <v>24526</v>
+        <v>35484</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>24561</v>
+        <v>35559</v>
       </c>
       <c r="I75" s="16">
         <f>H75-G75</f>
@@ -2466,10 +2470,10 @@
         <v>50</v>
       </c>
       <c r="B76" s="14" t="n">
-        <v>45828</v>
+        <v>46192</v>
       </c>
       <c r="C76" s="14" t="n">
-        <v>45828</v>
+        <v>46192</v>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
@@ -2478,19 +2482,19 @@
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Multi-drop delivery round</t>
+          <t>Rideshare fares - evening shift</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>Aspley</t>
+          <t>Marrickville</t>
         </is>
       </c>
       <c r="G76" s="16" t="n">
-        <v>24561</v>
+        <v>35559</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>24692</v>
+        <v>35729</v>
       </c>
       <c r="I76" s="16">
         <f>H76-G76</f>
@@ -2502,31 +2506,27 @@
         <v>51</v>
       </c>
       <c r="B77" s="14" t="n">
-        <v>45829</v>
+        <v>46192</v>
       </c>
       <c r="C77" s="14" t="n">
-        <v>45829</v>
+        <v>46192</v>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - weekend shift</t>
-        </is>
-      </c>
-      <c r="F77" s="15" t="inlineStr">
-        <is>
-          <t>Chermside</t>
-        </is>
-      </c>
+          <t>Private use - personal errands</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr"/>
       <c r="G77" s="16" t="n">
-        <v>24692</v>
+        <v>35729</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>24856</v>
+        <v>35780</v>
       </c>
       <c r="I77" s="16">
         <f>H77-G77</f>
@@ -2538,27 +2538,31 @@
         <v>52</v>
       </c>
       <c r="B78" s="14" t="n">
-        <v>45829</v>
+        <v>46193</v>
       </c>
       <c r="C78" s="14" t="n">
-        <v>45829</v>
+        <v>46193</v>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
-        </is>
-      </c>
-      <c r="F78" s="15" t="inlineStr"/>
+          <t>Rideshare fares - event and venue pickups</t>
+        </is>
+      </c>
+      <c r="F78" s="15" t="inlineStr">
+        <is>
+          <t>Castle Hill</t>
+        </is>
+      </c>
       <c r="G78" s="16" t="n">
-        <v>24856</v>
+        <v>35780</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>24887</v>
+        <v>35993</v>
       </c>
       <c r="I78" s="16">
         <f>H78-G78</f>
@@ -2570,10 +2574,10 @@
         <v>53</v>
       </c>
       <c r="B79" s="14" t="n">
-        <v>45830</v>
+        <v>46194</v>
       </c>
       <c r="C79" s="14" t="n">
-        <v>45830</v>
+        <v>46194</v>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
@@ -2582,19 +2586,19 @@
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>Parcel delivery run</t>
+          <t>Rideshare fares - suburban runs</t>
         </is>
       </c>
       <c r="F79" s="15" t="inlineStr">
         <is>
-          <t>Toowong / Sunnybank</t>
+          <t>Marrickville / Castle Hill</t>
         </is>
       </c>
       <c r="G79" s="16" t="n">
-        <v>24887</v>
+        <v>35993</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>25116</v>
+        <v>36291</v>
       </c>
       <c r="I79" s="16">
         <f>H79-G79</f>
@@ -2606,10 +2610,10 @@
         <v>54</v>
       </c>
       <c r="B80" s="14" t="n">
-        <v>45830</v>
+        <v>46194</v>
       </c>
       <c r="C80" s="14" t="n">
-        <v>45830</v>
+        <v>46194</v>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
@@ -2623,10 +2627,10 @@
       </c>
       <c r="F80" s="15" t="inlineStr"/>
       <c r="G80" s="16" t="n">
-        <v>25116</v>
+        <v>36291</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>25156</v>
+        <v>36336</v>
       </c>
       <c r="I80" s="16">
         <f>H80-G80</f>
@@ -2638,10 +2642,10 @@
         <v>55</v>
       </c>
       <c r="B81" s="14" t="n">
-        <v>45831</v>
+        <v>46195</v>
       </c>
       <c r="C81" s="14" t="n">
-        <v>45831</v>
+        <v>46195</v>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
@@ -2655,10 +2659,10 @@
       </c>
       <c r="F81" s="15" t="inlineStr"/>
       <c r="G81" s="16" t="n">
-        <v>25156</v>
+        <v>36336</v>
       </c>
       <c r="H81" s="16" t="n">
-        <v>25223</v>
+        <v>36371</v>
       </c>
       <c r="I81" s="16">
         <f>H81-G81</f>
@@ -2670,27 +2674,31 @@
         <v>56</v>
       </c>
       <c r="B82" s="14" t="n">
-        <v>45833</v>
+        <v>46199</v>
       </c>
       <c r="C82" s="14" t="n">
-        <v>45833</v>
+        <v>46199</v>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
-        </is>
-      </c>
-      <c r="F82" s="15" t="inlineStr"/>
+          <t>Rideshare fares - weekend shift</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr">
+        <is>
+          <t>Newtown</t>
+        </is>
+      </c>
       <c r="G82" s="16" t="n">
-        <v>25223</v>
+        <v>36371</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>25295</v>
+        <v>36604</v>
       </c>
       <c r="I82" s="16">
         <f>H82-G82</f>
@@ -2702,10 +2710,10 @@
         <v>57</v>
       </c>
       <c r="B83" s="14" t="n">
-        <v>45834</v>
+        <v>46199</v>
       </c>
       <c r="C83" s="14" t="n">
-        <v>45834</v>
+        <v>46199</v>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
@@ -2714,15 +2722,15 @@
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>Private use - shopping trip</t>
+          <t>Private use - personal errands</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr"/>
       <c r="G83" s="16" t="n">
-        <v>25295</v>
+        <v>36604</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>25344</v>
+        <v>36678</v>
       </c>
       <c r="I83" s="16">
         <f>H83-G83</f>
@@ -2734,10 +2742,10 @@
         <v>58</v>
       </c>
       <c r="B84" s="14" t="n">
-        <v>45835</v>
+        <v>46200</v>
       </c>
       <c r="C84" s="14" t="n">
-        <v>45835</v>
+        <v>46200</v>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
@@ -2746,19 +2754,19 @@
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - airport transfers</t>
+          <t>Rideshare fares - late night runs</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>Fortitude Valley</t>
+          <t>Parramatta</t>
         </is>
       </c>
       <c r="G84" s="16" t="n">
-        <v>25344</v>
+        <v>36678</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>25524</v>
+        <v>36913</v>
       </c>
       <c r="I84" s="16">
         <f>H84-G84</f>
@@ -2770,27 +2778,31 @@
         <v>59</v>
       </c>
       <c r="B85" s="14" t="n">
-        <v>45835</v>
+        <v>46201</v>
       </c>
       <c r="C85" s="14" t="n">
-        <v>45835</v>
+        <v>46201</v>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
-        </is>
-      </c>
-      <c r="F85" s="15" t="inlineStr"/>
+          <t>Rideshare fares - weekend shift</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr">
+        <is>
+          <t>Randwick</t>
+        </is>
+      </c>
       <c r="G85" s="16" t="n">
-        <v>25524</v>
+        <v>36913</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>25563</v>
+        <v>37109</v>
       </c>
       <c r="I85" s="16">
         <f>H85-G85</f>
@@ -2802,31 +2814,27 @@
         <v>60</v>
       </c>
       <c r="B86" s="14" t="n">
-        <v>45836</v>
+        <v>46201</v>
       </c>
       <c r="C86" s="14" t="n">
-        <v>45836</v>
+        <v>46201</v>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Courier pickups and drop-offs</t>
-        </is>
-      </c>
-      <c r="F86" s="15" t="inlineStr">
-        <is>
-          <t>Sunnybank</t>
-        </is>
-      </c>
+          <t>Private use - weekend outing</t>
+        </is>
+      </c>
+      <c r="F86" s="15" t="inlineStr"/>
       <c r="G86" s="16" t="n">
-        <v>25563</v>
+        <v>37109</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>25743</v>
+        <v>37185</v>
       </c>
       <c r="I86" s="16">
         <f>H86-G86</f>
@@ -2834,180 +2842,146 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="13" t="n">
-        <v>61</v>
-      </c>
-      <c r="B87" s="14" t="n">
-        <v>45837</v>
-      </c>
-      <c r="C87" s="14" t="n">
-        <v>45837</v>
-      </c>
-      <c r="D87" s="13" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="E87" s="15" t="inlineStr">
-        <is>
-          <t>Rideshare fares - late night runs</t>
-        </is>
-      </c>
-      <c r="F87" s="15" t="inlineStr">
-        <is>
-          <t>South Bank</t>
-        </is>
-      </c>
-      <c r="G87" s="16" t="n">
-        <v>25743</v>
-      </c>
-      <c r="H87" s="16" t="n">
-        <v>25894</v>
-      </c>
-      <c r="I87" s="16">
-        <f>H87-G87</f>
+      <c r="A87" s="17" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B87" s="15" t="n"/>
+      <c r="C87" s="15" t="n"/>
+      <c r="D87" s="15" t="n"/>
+      <c r="E87" s="15" t="n"/>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>Total kilometres</t>
+        </is>
+      </c>
+      <c r="G87" s="15" t="n"/>
+      <c r="H87" s="15" t="n"/>
+      <c r="I87" s="19">
+        <f>SUM(I27:I86)</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="13" t="n">
-        <v>62</v>
-      </c>
-      <c r="B88" s="14" t="n">
-        <v>45838</v>
-      </c>
-      <c r="C88" s="14" t="n">
-        <v>45838</v>
-      </c>
-      <c r="D88" s="13" t="inlineStr">
-        <is>
-          <t>Private</t>
-        </is>
-      </c>
-      <c r="E88" s="15" t="inlineStr">
-        <is>
-          <t>Private use - weekend outing</t>
-        </is>
-      </c>
-      <c r="F88" s="15" t="inlineStr"/>
-      <c r="G88" s="16" t="n">
-        <v>25894</v>
-      </c>
-      <c r="H88" s="16" t="n">
-        <v>25954</v>
-      </c>
-      <c r="I88" s="16">
-        <f>H88-G88</f>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>Business kilometres</t>
+        </is>
+      </c>
+      <c r="I88" s="19">
+        <f>SUMIF($D$27:$D$86,"Business",$I$27:$I$86)</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="17" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B89" s="15" t="n"/>
-      <c r="C89" s="15" t="n"/>
-      <c r="D89" s="15" t="n"/>
-      <c r="E89" s="15" t="n"/>
       <c r="F89" s="18" t="inlineStr">
         <is>
-          <t>Total kilometres</t>
-        </is>
-      </c>
-      <c r="G89" s="15" t="n"/>
-      <c r="H89" s="15" t="n"/>
+          <t>Private kilometres</t>
+        </is>
+      </c>
       <c r="I89" s="19">
-        <f>SUM(I27:I88)</f>
+        <f>SUMIF($D$27:$D$86,"Private",$I$27:$I$86)</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="F90" s="18" t="inlineStr">
         <is>
-          <t>Business kilometres</t>
-        </is>
-      </c>
-      <c r="I90" s="19">
-        <f>SUMIF($D$27:$D$88,"Business",$I$27:$I$88)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="F91" s="18" t="inlineStr">
-        <is>
-          <t>Private kilometres</t>
-        </is>
-      </c>
-      <c r="I91" s="19">
-        <f>SUMIF($D$27:$D$88,"Private",$I$27:$I$88)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="F92" s="18" t="inlineStr">
-        <is>
           <t>Business-use percentage</t>
         </is>
       </c>
-      <c r="I92" s="20">
-        <f>IFERROR(I90/I89,0)</f>
-        <v/>
+      <c r="I90" s="20">
+        <f>IFERROR(I88/I87,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Odometer readings for each income year</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="n"/>
+    </row>
+    <row r="94" ht="30" customHeight="1">
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>Income year</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>Odometer at start of year</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Odometer at end of year</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="inlineStr">
+        <is>
+          <t>Total km for the year</t>
+        </is>
+      </c>
+      <c r="F94" s="12" t="inlineStr">
+        <is>
+          <t>Business km at the logbook percentage</t>
+        </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
-        <is>
-          <t>Odometer readings for each income year</t>
-        </is>
-      </c>
-      <c r="B95" s="4" t="n"/>
-      <c r="C95" s="4" t="n"/>
-      <c r="D95" s="4" t="n"/>
-      <c r="E95" s="4" t="n"/>
-      <c r="F95" s="4" t="n"/>
-      <c r="G95" s="4" t="n"/>
-      <c r="H95" s="4" t="n"/>
-      <c r="I95" s="4" t="n"/>
-    </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="B96" s="12" t="inlineStr">
-        <is>
-          <t>Income year</t>
-        </is>
-      </c>
-      <c r="C96" s="12" t="inlineStr">
-        <is>
-          <t>Odometer at start of year</t>
-        </is>
-      </c>
-      <c r="D96" s="12" t="inlineStr">
-        <is>
-          <t>Odometer at end of year</t>
-        </is>
-      </c>
-      <c r="E96" s="12" t="inlineStr">
-        <is>
-          <t>Total km for the year</t>
-        </is>
-      </c>
-      <c r="F96" s="12" t="inlineStr">
-        <is>
-          <t>Business km at the logbook percentage</t>
-        </is>
+      <c r="B95" s="13" t="inlineStr">
+        <is>
+          <t>2025-26</t>
+        </is>
+      </c>
+      <c r="C95" s="16" t="n"/>
+      <c r="D95" s="16" t="n">
+        <v>37185</v>
+      </c>
+      <c r="E95" s="16">
+        <f>IF(COUNT(C95:D95)=2,D95-C95,"")</f>
+        <v/>
+      </c>
+      <c r="F95" s="16">
+        <f>IF(ISNUMBER(E95),ROUND(E95*$D$23,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="13" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
+      </c>
+      <c r="C96" s="16" t="n"/>
+      <c r="D96" s="16" t="n"/>
+      <c r="E96" s="16">
+        <f>IF(COUNT(C96:D96)=2,D96-C96,"")</f>
+        <v/>
+      </c>
+      <c r="F96" s="16">
+        <f>IF(ISNUMBER(E96),ROUND(E96*$D$23,0),"")</f>
+        <v/>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>2024-25</t>
+          <t>2027-28</t>
         </is>
       </c>
       <c r="C97" s="16" t="n"/>
-      <c r="D97" s="16" t="n">
-        <v>25954</v>
-      </c>
+      <c r="D97" s="16" t="n"/>
       <c r="E97" s="16">
         <f>IF(COUNT(C97:D97)=2,D97-C97,"")</f>
         <v/>
@@ -3020,7 +2994,7 @@
     <row r="98">
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>2025-26</t>
+          <t>2028-29</t>
         </is>
       </c>
       <c r="C98" s="16" t="n"/>
@@ -3037,7 +3011,7 @@
     <row r="99">
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>2026-27</t>
+          <t>2029-30</t>
         </is>
       </c>
       <c r="C99" s="16" t="n"/>
@@ -3048,40 +3022,6 @@
       </c>
       <c r="F99" s="16">
         <f>IF(ISNUMBER(E99),ROUND(E99*$D$23,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="13" t="inlineStr">
-        <is>
-          <t>2027-28</t>
-        </is>
-      </c>
-      <c r="C100" s="16" t="n"/>
-      <c r="D100" s="16" t="n"/>
-      <c r="E100" s="16">
-        <f>IF(COUNT(C100:D100)=2,D100-C100,"")</f>
-        <v/>
-      </c>
-      <c r="F100" s="16">
-        <f>IF(ISNUMBER(E100),ROUND(E100*$D$23,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="13" t="inlineStr">
-        <is>
-          <t>2028-29</t>
-        </is>
-      </c>
-      <c r="C101" s="16" t="n"/>
-      <c r="D101" s="16" t="n"/>
-      <c r="E101" s="16">
-        <f>IF(COUNT(C101:D101)=2,D101-C101,"")</f>
-        <v/>
-      </c>
-      <c r="F101" s="16">
-        <f>IF(ISNUMBER(E101),ROUND(E101*$D$23,0),"")</f>
         <v/>
       </c>
     </row>
@@ -3093,7 +3033,6 @@
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="D16:I16"/>
     <mergeCell ref="D7:I7"/>
-    <mergeCell ref="A95:I95"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A23:C23"/>
@@ -3113,6 +3052,7 @@
     <mergeCell ref="D14:I14"/>
     <mergeCell ref="D5:I5"/>
     <mergeCell ref="D23:I23"/>
+    <mergeCell ref="A93:I93"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="D20:I20"/>
     <mergeCell ref="A15:C15"/>
@@ -3137,7 +3077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I102"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3188,7 +3128,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Yash Vadukiya</t>
+          <t>Sam Taylor</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3152,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>Corolla Hybrid</t>
+          <t>Corolla</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3188,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>ABC123</t>
+          <t>XYZ789</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3214,7 @@
         </is>
       </c>
       <c r="D13" s="7" t="n">
-        <v>45839</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="14">
@@ -3284,7 +3224,7 @@
         </is>
       </c>
       <c r="D14" s="7" t="n">
-        <v>45900</v>
+        <v>46282</v>
       </c>
     </row>
     <row r="15">
@@ -3294,7 +3234,7 @@
         </is>
       </c>
       <c r="D15" s="8" t="n">
-        <v>25954</v>
+        <v>37185</v>
       </c>
     </row>
     <row r="16">
@@ -3304,7 +3244,7 @@
         </is>
       </c>
       <c r="D16" s="8" t="n">
-        <v>32000</v>
+        <v>46500</v>
       </c>
     </row>
     <row r="17">
@@ -3340,7 +3280,7 @@
         </is>
       </c>
       <c r="D20" s="10" t="n">
-        <v>8000</v>
+        <v>13346.66666666667</v>
       </c>
     </row>
     <row r="21">
@@ -3350,7 +3290,7 @@
         </is>
       </c>
       <c r="D21" s="8">
-        <f>I91</f>
+        <f>I109</f>
         <v/>
       </c>
     </row>
@@ -3361,7 +3301,7 @@
         </is>
       </c>
       <c r="D22" s="8">
-        <f>I92</f>
+        <f>I110</f>
         <v/>
       </c>
     </row>
@@ -3439,10 +3379,10 @@
         <v>1</v>
       </c>
       <c r="B27" s="14" t="n">
-        <v>45839</v>
+        <v>46204</v>
       </c>
       <c r="C27" s="14" t="n">
-        <v>45839</v>
+        <v>46204</v>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
@@ -3451,15 +3391,15 @@
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F27" s="15" t="inlineStr"/>
       <c r="G27" s="16" t="n">
-        <v>25954</v>
+        <v>37185</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>25991</v>
+        <v>37261</v>
       </c>
       <c r="I27" s="16">
         <f>H27-G27</f>
@@ -3471,10 +3411,10 @@
         <v>2</v>
       </c>
       <c r="B28" s="14" t="n">
-        <v>45840</v>
+        <v>46205</v>
       </c>
       <c r="C28" s="14" t="n">
-        <v>45840</v>
+        <v>46205</v>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
@@ -3483,15 +3423,15 @@
       </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
-          <t>Private use - shopping trip</t>
+          <t>Private use - family travel</t>
         </is>
       </c>
       <c r="F28" s="15" t="inlineStr"/>
       <c r="G28" s="16" t="n">
-        <v>25991</v>
+        <v>37261</v>
       </c>
       <c r="H28" s="16" t="n">
-        <v>26066</v>
+        <v>37299</v>
       </c>
       <c r="I28" s="16">
         <f>H28-G28</f>
@@ -3503,27 +3443,31 @@
         <v>3</v>
       </c>
       <c r="B29" s="14" t="n">
-        <v>45841</v>
+        <v>46206</v>
       </c>
       <c r="C29" s="14" t="n">
-        <v>45841</v>
+        <v>46206</v>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>Private use - shopping trip</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr"/>
+          <t>Rideshare fares - airport transfers</t>
+        </is>
+      </c>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>Pyrmont / Surry Hills</t>
+        </is>
+      </c>
       <c r="G29" s="16" t="n">
-        <v>26066</v>
+        <v>37299</v>
       </c>
       <c r="H29" s="16" t="n">
-        <v>26138</v>
+        <v>37550</v>
       </c>
       <c r="I29" s="16">
         <f>H29-G29</f>
@@ -3535,31 +3479,27 @@
         <v>4</v>
       </c>
       <c r="B30" s="14" t="n">
-        <v>45842</v>
+        <v>46206</v>
       </c>
       <c r="C30" s="14" t="n">
-        <v>45842</v>
+        <v>46206</v>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
         <is>
-          <t>Food delivery run</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
-        <is>
-          <t>North Lakes / Newstead</t>
-        </is>
-      </c>
+          <t>Private use - shopping trip</t>
+        </is>
+      </c>
+      <c r="F30" s="15" t="inlineStr"/>
       <c r="G30" s="16" t="n">
-        <v>26138</v>
+        <v>37550</v>
       </c>
       <c r="H30" s="16" t="n">
-        <v>26358</v>
+        <v>37589</v>
       </c>
       <c r="I30" s="16">
         <f>H30-G30</f>
@@ -3571,27 +3511,31 @@
         <v>5</v>
       </c>
       <c r="B31" s="14" t="n">
-        <v>45842</v>
+        <v>46207</v>
       </c>
       <c r="C31" s="14" t="n">
-        <v>45842</v>
+        <v>46207</v>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>Private use - shopping trip</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr"/>
+          <t>Rideshare fares - event and venue pickups</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>Randwick</t>
+        </is>
+      </c>
       <c r="G31" s="16" t="n">
-        <v>26358</v>
+        <v>37589</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>26392</v>
+        <v>37741</v>
       </c>
       <c r="I31" s="16">
         <f>H31-G31</f>
@@ -3603,31 +3547,27 @@
         <v>6</v>
       </c>
       <c r="B32" s="14" t="n">
-        <v>45843</v>
+        <v>46207</v>
       </c>
       <c r="C32" s="14" t="n">
-        <v>45843</v>
+        <v>46207</v>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - weekend shift</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>Springwood / Fortitude Valley</t>
-        </is>
-      </c>
+          <t>Private use - family travel</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr"/>
       <c r="G32" s="16" t="n">
-        <v>26392</v>
+        <v>37741</v>
       </c>
       <c r="H32" s="16" t="n">
-        <v>26602</v>
+        <v>37772</v>
       </c>
       <c r="I32" s="16">
         <f>H32-G32</f>
@@ -3639,27 +3579,31 @@
         <v>7</v>
       </c>
       <c r="B33" s="14" t="n">
-        <v>45843</v>
+        <v>46208</v>
       </c>
       <c r="C33" s="14" t="n">
-        <v>45843</v>
+        <v>46208</v>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
-        </is>
-      </c>
-      <c r="F33" s="15" t="inlineStr"/>
+          <t>Rideshare fares - morning peak</t>
+        </is>
+      </c>
+      <c r="F33" s="15" t="inlineStr">
+        <is>
+          <t>Castle Hill</t>
+        </is>
+      </c>
       <c r="G33" s="16" t="n">
-        <v>26602</v>
+        <v>37772</v>
       </c>
       <c r="H33" s="16" t="n">
-        <v>26635</v>
+        <v>37889</v>
       </c>
       <c r="I33" s="16">
         <f>H33-G33</f>
@@ -3671,31 +3615,27 @@
         <v>8</v>
       </c>
       <c r="B34" s="14" t="n">
-        <v>45844</v>
+        <v>46208</v>
       </c>
       <c r="C34" s="14" t="n">
-        <v>45844</v>
+        <v>46208</v>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>Parcel delivery run</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>Sunnybank</t>
-        </is>
-      </c>
+          <t>Private use - shopping trip</t>
+        </is>
+      </c>
+      <c r="F34" s="15" t="inlineStr"/>
       <c r="G34" s="16" t="n">
-        <v>26635</v>
+        <v>37889</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>26762</v>
+        <v>37939</v>
       </c>
       <c r="I34" s="16">
         <f>H34-G34</f>
@@ -3707,10 +3647,10 @@
         <v>9</v>
       </c>
       <c r="B35" s="14" t="n">
-        <v>45846</v>
+        <v>46210</v>
       </c>
       <c r="C35" s="14" t="n">
-        <v>45846</v>
+        <v>46210</v>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
@@ -3719,15 +3659,15 @@
       </c>
       <c r="E35" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F35" s="15" t="inlineStr"/>
       <c r="G35" s="16" t="n">
-        <v>26762</v>
+        <v>37939</v>
       </c>
       <c r="H35" s="16" t="n">
-        <v>26839</v>
+        <v>38015</v>
       </c>
       <c r="I35" s="16">
         <f>H35-G35</f>
@@ -3739,10 +3679,10 @@
         <v>10</v>
       </c>
       <c r="B36" s="14" t="n">
-        <v>45848</v>
+        <v>46211</v>
       </c>
       <c r="C36" s="14" t="n">
-        <v>45848</v>
+        <v>46211</v>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
@@ -3751,15 +3691,15 @@
       </c>
       <c r="E36" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F36" s="15" t="inlineStr"/>
       <c r="G36" s="16" t="n">
-        <v>26839</v>
+        <v>38015</v>
       </c>
       <c r="H36" s="16" t="n">
-        <v>26908</v>
+        <v>38057</v>
       </c>
       <c r="I36" s="16">
         <f>H36-G36</f>
@@ -3771,31 +3711,27 @@
         <v>11</v>
       </c>
       <c r="B37" s="14" t="n">
-        <v>45849</v>
+        <v>46212</v>
       </c>
       <c r="C37" s="14" t="n">
-        <v>45849</v>
+        <v>46212</v>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - weekend shift</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="inlineStr">
-        <is>
-          <t>Brisbane Airport</t>
-        </is>
-      </c>
+          <t>Private use - personal errands</t>
+        </is>
+      </c>
+      <c r="F37" s="15" t="inlineStr"/>
       <c r="G37" s="16" t="n">
-        <v>26908</v>
+        <v>38057</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>27006</v>
+        <v>38092</v>
       </c>
       <c r="I37" s="16">
         <f>H37-G37</f>
@@ -3807,27 +3743,31 @@
         <v>12</v>
       </c>
       <c r="B38" s="14" t="n">
-        <v>45849</v>
+        <v>46213</v>
       </c>
       <c r="C38" s="14" t="n">
-        <v>45849</v>
+        <v>46213</v>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
-        </is>
-      </c>
-      <c r="F38" s="15" t="inlineStr"/>
+          <t>Rideshare fares - late night runs</t>
+        </is>
+      </c>
+      <c r="F38" s="15" t="inlineStr">
+        <is>
+          <t>Newtown</t>
+        </is>
+      </c>
       <c r="G38" s="16" t="n">
-        <v>27006</v>
+        <v>38092</v>
       </c>
       <c r="H38" s="16" t="n">
-        <v>27065</v>
+        <v>38260</v>
       </c>
       <c r="I38" s="16">
         <f>H38-G38</f>
@@ -3839,31 +3779,27 @@
         <v>13</v>
       </c>
       <c r="B39" s="14" t="n">
-        <v>45850</v>
+        <v>46213</v>
       </c>
       <c r="C39" s="14" t="n">
-        <v>45850</v>
+        <v>46213</v>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>Food delivery - lunch peak</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="inlineStr">
-        <is>
-          <t>Aspley</t>
-        </is>
-      </c>
+          <t>Private use - personal travel</t>
+        </is>
+      </c>
+      <c r="F39" s="15" t="inlineStr"/>
       <c r="G39" s="16" t="n">
-        <v>27065</v>
+        <v>38260</v>
       </c>
       <c r="H39" s="16" t="n">
-        <v>27205</v>
+        <v>38337</v>
       </c>
       <c r="I39" s="16">
         <f>H39-G39</f>
@@ -3875,10 +3811,10 @@
         <v>14</v>
       </c>
       <c r="B40" s="14" t="n">
-        <v>45851</v>
+        <v>46214</v>
       </c>
       <c r="C40" s="14" t="n">
-        <v>45851</v>
+        <v>46214</v>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
@@ -3887,19 +3823,19 @@
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - morning peak</t>
+          <t>Rideshare fares - suburban runs</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>Brisbane CBD</t>
+          <t>Marrickville</t>
         </is>
       </c>
       <c r="G40" s="16" t="n">
-        <v>27205</v>
+        <v>38337</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>27338</v>
+        <v>38496</v>
       </c>
       <c r="I40" s="16">
         <f>H40-G40</f>
@@ -3911,10 +3847,10 @@
         <v>15</v>
       </c>
       <c r="B41" s="14" t="n">
-        <v>45851</v>
+        <v>46214</v>
       </c>
       <c r="C41" s="14" t="n">
-        <v>45851</v>
+        <v>46214</v>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
@@ -3923,15 +3859,15 @@
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
+          <t>Private use - family travel</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr"/>
       <c r="G41" s="16" t="n">
-        <v>27338</v>
+        <v>38496</v>
       </c>
       <c r="H41" s="16" t="n">
-        <v>27378</v>
+        <v>38566</v>
       </c>
       <c r="I41" s="16">
         <f>H41-G41</f>
@@ -3943,27 +3879,31 @@
         <v>16</v>
       </c>
       <c r="B42" s="14" t="n">
-        <v>45852</v>
+        <v>46215</v>
       </c>
       <c r="C42" s="14" t="n">
-        <v>45852</v>
+        <v>46215</v>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>Private use - shopping trip</t>
-        </is>
-      </c>
-      <c r="F42" s="15" t="inlineStr"/>
+          <t>Rideshare fares - weekend shift</t>
+        </is>
+      </c>
+      <c r="F42" s="15" t="inlineStr">
+        <is>
+          <t>Castle Hill</t>
+        </is>
+      </c>
       <c r="G42" s="16" t="n">
-        <v>27378</v>
+        <v>38566</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>27450</v>
+        <v>38715</v>
       </c>
       <c r="I42" s="16">
         <f>H42-G42</f>
@@ -3975,10 +3915,10 @@
         <v>17</v>
       </c>
       <c r="B43" s="14" t="n">
-        <v>45855</v>
+        <v>46215</v>
       </c>
       <c r="C43" s="14" t="n">
-        <v>45855</v>
+        <v>46215</v>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
@@ -3987,15 +3927,15 @@
       </c>
       <c r="E43" s="15" t="inlineStr">
         <is>
-          <t>Private use - shopping trip</t>
+          <t>Private use - personal errands</t>
         </is>
       </c>
       <c r="F43" s="15" t="inlineStr"/>
       <c r="G43" s="16" t="n">
-        <v>27450</v>
+        <v>38715</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>27481</v>
+        <v>38760</v>
       </c>
       <c r="I43" s="16">
         <f>H43-G43</f>
@@ -4007,31 +3947,27 @@
         <v>18</v>
       </c>
       <c r="B44" s="14" t="n">
-        <v>45856</v>
+        <v>46216</v>
       </c>
       <c r="C44" s="14" t="n">
-        <v>45856</v>
+        <v>46216</v>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
         <is>
-          <t>Late night delivery run</t>
-        </is>
-      </c>
-      <c r="F44" s="15" t="inlineStr">
-        <is>
-          <t>Mount Gravatt</t>
-        </is>
-      </c>
+          <t>Private use - personal travel</t>
+        </is>
+      </c>
+      <c r="F44" s="15" t="inlineStr"/>
       <c r="G44" s="16" t="n">
-        <v>27481</v>
+        <v>38760</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>27606</v>
+        <v>38811</v>
       </c>
       <c r="I44" s="16">
         <f>H44-G44</f>
@@ -4043,10 +3979,10 @@
         <v>19</v>
       </c>
       <c r="B45" s="14" t="n">
-        <v>45856</v>
+        <v>46217</v>
       </c>
       <c r="C45" s="14" t="n">
-        <v>45856</v>
+        <v>46217</v>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
@@ -4055,15 +3991,15 @@
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal travel</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr"/>
       <c r="G45" s="16" t="n">
-        <v>27606</v>
+        <v>38811</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>27662</v>
+        <v>38876</v>
       </c>
       <c r="I45" s="16">
         <f>H45-G45</f>
@@ -4075,31 +4011,27 @@
         <v>20</v>
       </c>
       <c r="B46" s="14" t="n">
-        <v>45857</v>
+        <v>46218</v>
       </c>
       <c r="C46" s="14" t="n">
-        <v>45857</v>
+        <v>46218</v>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - morning peak</t>
-        </is>
-      </c>
-      <c r="F46" s="15" t="inlineStr">
-        <is>
-          <t>Logan Central / West End</t>
-        </is>
-      </c>
+          <t>Private use - personal errands</t>
+        </is>
+      </c>
+      <c r="F46" s="15" t="inlineStr"/>
       <c r="G46" s="16" t="n">
-        <v>27662</v>
+        <v>38876</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>27898</v>
+        <v>38921</v>
       </c>
       <c r="I46" s="16">
         <f>H46-G46</f>
@@ -4111,10 +4043,10 @@
         <v>21</v>
       </c>
       <c r="B47" s="14" t="n">
-        <v>45858</v>
+        <v>46220</v>
       </c>
       <c r="C47" s="14" t="n">
-        <v>45858</v>
+        <v>46220</v>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
@@ -4123,19 +4055,19 @@
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>Late night delivery run</t>
+          <t>Rideshare fares - suburban runs</t>
         </is>
       </c>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>Indooroopilly / North Lakes</t>
+          <t>Sydney Airport / Sydney CBD</t>
         </is>
       </c>
       <c r="G47" s="16" t="n">
-        <v>27898</v>
+        <v>38921</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>28124</v>
+        <v>39203</v>
       </c>
       <c r="I47" s="16">
         <f>H47-G47</f>
@@ -4147,10 +4079,10 @@
         <v>22</v>
       </c>
       <c r="B48" s="14" t="n">
-        <v>45858</v>
+        <v>46220</v>
       </c>
       <c r="C48" s="14" t="n">
-        <v>45858</v>
+        <v>46220</v>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
@@ -4159,15 +4091,15 @@
       </c>
       <c r="E48" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
+          <t>Private use - personal errands</t>
         </is>
       </c>
       <c r="F48" s="15" t="inlineStr"/>
       <c r="G48" s="16" t="n">
-        <v>28124</v>
+        <v>39203</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>28168</v>
+        <v>39263</v>
       </c>
       <c r="I48" s="16">
         <f>H48-G48</f>
@@ -4179,27 +4111,31 @@
         <v>23</v>
       </c>
       <c r="B49" s="14" t="n">
-        <v>45860</v>
+        <v>46221</v>
       </c>
       <c r="C49" s="14" t="n">
-        <v>45860</v>
+        <v>46221</v>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
-        </is>
-      </c>
-      <c r="F49" s="15" t="inlineStr"/>
+          <t>Rideshare fares - airport transfers</t>
+        </is>
+      </c>
+      <c r="F49" s="15" t="inlineStr">
+        <is>
+          <t>Sydney CBD / Sydney Airport</t>
+        </is>
+      </c>
       <c r="G49" s="16" t="n">
-        <v>28168</v>
+        <v>39263</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>28233</v>
+        <v>39533</v>
       </c>
       <c r="I49" s="16">
         <f>H49-G49</f>
@@ -4211,10 +4147,10 @@
         <v>24</v>
       </c>
       <c r="B50" s="14" t="n">
-        <v>45861</v>
+        <v>46221</v>
       </c>
       <c r="C50" s="14" t="n">
-        <v>45861</v>
+        <v>46221</v>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
@@ -4223,15 +4159,15 @@
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
+          <t>Private use - personal errands</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr"/>
       <c r="G50" s="16" t="n">
-        <v>28233</v>
+        <v>39533</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>28279</v>
+        <v>39600</v>
       </c>
       <c r="I50" s="16">
         <f>H50-G50</f>
@@ -4243,27 +4179,31 @@
         <v>25</v>
       </c>
       <c r="B51" s="14" t="n">
-        <v>45862</v>
+        <v>46222</v>
       </c>
       <c r="C51" s="14" t="n">
-        <v>45862</v>
+        <v>46222</v>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
-        </is>
-      </c>
-      <c r="F51" s="15" t="inlineStr"/>
+          <t>Rideshare fares - late night runs</t>
+        </is>
+      </c>
+      <c r="F51" s="15" t="inlineStr">
+        <is>
+          <t>Marrickville</t>
+        </is>
+      </c>
       <c r="G51" s="16" t="n">
-        <v>28279</v>
+        <v>39600</v>
       </c>
       <c r="H51" s="16" t="n">
-        <v>28354</v>
+        <v>39768</v>
       </c>
       <c r="I51" s="16">
         <f>H51-G51</f>
@@ -4275,31 +4215,27 @@
         <v>26</v>
       </c>
       <c r="B52" s="14" t="n">
-        <v>45863</v>
+        <v>46222</v>
       </c>
       <c r="C52" s="14" t="n">
-        <v>45863</v>
+        <v>46222</v>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - weekend shift</t>
-        </is>
-      </c>
-      <c r="F52" s="15" t="inlineStr">
-        <is>
-          <t>Chermside</t>
-        </is>
-      </c>
+          <t>Private use - personal errands</t>
+        </is>
+      </c>
+      <c r="F52" s="15" t="inlineStr"/>
       <c r="G52" s="16" t="n">
-        <v>28354</v>
+        <v>39768</v>
       </c>
       <c r="H52" s="16" t="n">
-        <v>28494</v>
+        <v>39838</v>
       </c>
       <c r="I52" s="16">
         <f>H52-G52</f>
@@ -4311,10 +4247,10 @@
         <v>27</v>
       </c>
       <c r="B53" s="14" t="n">
-        <v>45863</v>
+        <v>46223</v>
       </c>
       <c r="C53" s="14" t="n">
-        <v>45863</v>
+        <v>46223</v>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
@@ -4323,15 +4259,15 @@
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F53" s="15" t="inlineStr"/>
       <c r="G53" s="16" t="n">
-        <v>28494</v>
+        <v>39838</v>
       </c>
       <c r="H53" s="16" t="n">
-        <v>28519</v>
+        <v>39897</v>
       </c>
       <c r="I53" s="16">
         <f>H53-G53</f>
@@ -4343,31 +4279,27 @@
         <v>28</v>
       </c>
       <c r="B54" s="14" t="n">
-        <v>45864</v>
+        <v>46225</v>
       </c>
       <c r="C54" s="14" t="n">
-        <v>45864</v>
+        <v>46225</v>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>Late night delivery run</t>
-        </is>
-      </c>
-      <c r="F54" s="15" t="inlineStr">
-        <is>
-          <t>Mount Gravatt / Everton Park</t>
-        </is>
-      </c>
+          <t>Private use - family travel</t>
+        </is>
+      </c>
+      <c r="F54" s="15" t="inlineStr"/>
       <c r="G54" s="16" t="n">
-        <v>28519</v>
+        <v>39897</v>
       </c>
       <c r="H54" s="16" t="n">
-        <v>28711</v>
+        <v>39951</v>
       </c>
       <c r="I54" s="16">
         <f>H54-G54</f>
@@ -4379,31 +4311,27 @@
         <v>29</v>
       </c>
       <c r="B55" s="14" t="n">
-        <v>45865</v>
+        <v>46226</v>
       </c>
       <c r="C55" s="14" t="n">
-        <v>45865</v>
+        <v>46226</v>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - weekend shift</t>
-        </is>
-      </c>
-      <c r="F55" s="15" t="inlineStr">
-        <is>
-          <t>South Bank</t>
-        </is>
-      </c>
+          <t>Private use - personal errands</t>
+        </is>
+      </c>
+      <c r="F55" s="15" t="inlineStr"/>
       <c r="G55" s="16" t="n">
-        <v>28711</v>
+        <v>39951</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>28864</v>
+        <v>39999</v>
       </c>
       <c r="I55" s="16">
         <f>H55-G55</f>
@@ -4415,27 +4343,31 @@
         <v>30</v>
       </c>
       <c r="B56" s="14" t="n">
-        <v>45865</v>
+        <v>46227</v>
       </c>
       <c r="C56" s="14" t="n">
-        <v>45865</v>
+        <v>46227</v>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
-        </is>
-      </c>
-      <c r="F56" s="15" t="inlineStr"/>
+          <t>Rideshare fares - passenger trips</t>
+        </is>
+      </c>
+      <c r="F56" s="15" t="inlineStr">
+        <is>
+          <t>Pyrmont</t>
+        </is>
+      </c>
       <c r="G56" s="16" t="n">
-        <v>28864</v>
+        <v>39999</v>
       </c>
       <c r="H56" s="16" t="n">
-        <v>28925</v>
+        <v>40229</v>
       </c>
       <c r="I56" s="16">
         <f>H56-G56</f>
@@ -4447,10 +4379,10 @@
         <v>31</v>
       </c>
       <c r="B57" s="14" t="n">
-        <v>45869</v>
+        <v>46227</v>
       </c>
       <c r="C57" s="14" t="n">
-        <v>45869</v>
+        <v>46227</v>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
@@ -4459,15 +4391,15 @@
       </c>
       <c r="E57" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
+          <t>Private use - personal errands</t>
         </is>
       </c>
       <c r="F57" s="15" t="inlineStr"/>
       <c r="G57" s="16" t="n">
-        <v>28925</v>
+        <v>40229</v>
       </c>
       <c r="H57" s="16" t="n">
-        <v>28994</v>
+        <v>40293</v>
       </c>
       <c r="I57" s="16">
         <f>H57-G57</f>
@@ -4479,10 +4411,10 @@
         <v>32</v>
       </c>
       <c r="B58" s="14" t="n">
-        <v>45870</v>
+        <v>46228</v>
       </c>
       <c r="C58" s="14" t="n">
-        <v>45870</v>
+        <v>46228</v>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
@@ -4491,19 +4423,19 @@
       </c>
       <c r="E58" s="15" t="inlineStr">
         <is>
-          <t>Grocery delivery run</t>
+          <t>Rideshare fares - suburban runs</t>
         </is>
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>Aspley</t>
+          <t>Parramatta</t>
         </is>
       </c>
       <c r="G58" s="16" t="n">
-        <v>28994</v>
+        <v>40293</v>
       </c>
       <c r="H58" s="16" t="n">
-        <v>29179</v>
+        <v>40476</v>
       </c>
       <c r="I58" s="16">
         <f>H58-G58</f>
@@ -4515,10 +4447,10 @@
         <v>33</v>
       </c>
       <c r="B59" s="14" t="n">
-        <v>45870</v>
+        <v>46228</v>
       </c>
       <c r="C59" s="14" t="n">
-        <v>45870</v>
+        <v>46228</v>
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
@@ -4527,15 +4459,15 @@
       </c>
       <c r="E59" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
+          <t>Private use - weekend outing</t>
         </is>
       </c>
       <c r="F59" s="15" t="inlineStr"/>
       <c r="G59" s="16" t="n">
-        <v>29179</v>
+        <v>40476</v>
       </c>
       <c r="H59" s="16" t="n">
-        <v>29234</v>
+        <v>40531</v>
       </c>
       <c r="I59" s="16">
         <f>H59-G59</f>
@@ -4547,10 +4479,10 @@
         <v>34</v>
       </c>
       <c r="B60" s="14" t="n">
-        <v>45871</v>
+        <v>46229</v>
       </c>
       <c r="C60" s="14" t="n">
-        <v>45871</v>
+        <v>46229</v>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
@@ -4559,19 +4491,19 @@
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - late night runs</t>
+          <t>Rideshare fares - evening shift</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>Springwood</t>
+          <t>Newtown / Pyrmont</t>
         </is>
       </c>
       <c r="G60" s="16" t="n">
-        <v>29234</v>
+        <v>40531</v>
       </c>
       <c r="H60" s="16" t="n">
-        <v>29370</v>
+        <v>40808</v>
       </c>
       <c r="I60" s="16">
         <f>H60-G60</f>
@@ -4583,10 +4515,10 @@
         <v>35</v>
       </c>
       <c r="B61" s="14" t="n">
-        <v>45872</v>
+        <v>46234</v>
       </c>
       <c r="C61" s="14" t="n">
-        <v>45872</v>
+        <v>46234</v>
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
@@ -4595,19 +4527,19 @@
       </c>
       <c r="E61" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - weekend shift</t>
+          <t>Rideshare fares - passenger trips</t>
         </is>
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>Newstead</t>
+          <t>Castle Hill</t>
         </is>
       </c>
       <c r="G61" s="16" t="n">
-        <v>29370</v>
+        <v>40808</v>
       </c>
       <c r="H61" s="16" t="n">
-        <v>29459</v>
+        <v>41002</v>
       </c>
       <c r="I61" s="16">
         <f>H61-G61</f>
@@ -4619,27 +4551,31 @@
         <v>36</v>
       </c>
       <c r="B62" s="14" t="n">
-        <v>45872</v>
+        <v>46235</v>
       </c>
       <c r="C62" s="14" t="n">
-        <v>45872</v>
+        <v>46235</v>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal travel</t>
-        </is>
-      </c>
-      <c r="F62" s="15" t="inlineStr"/>
+          <t>Rideshare fares - passenger trips</t>
+        </is>
+      </c>
+      <c r="F62" s="15" t="inlineStr">
+        <is>
+          <t>Sydney Airport</t>
+        </is>
+      </c>
       <c r="G62" s="16" t="n">
-        <v>29459</v>
+        <v>41002</v>
       </c>
       <c r="H62" s="16" t="n">
-        <v>29519</v>
+        <v>41221</v>
       </c>
       <c r="I62" s="16">
         <f>H62-G62</f>
@@ -4651,27 +4587,31 @@
         <v>37</v>
       </c>
       <c r="B63" s="14" t="n">
-        <v>45873</v>
+        <v>46236</v>
       </c>
       <c r="C63" s="14" t="n">
-        <v>45873</v>
+        <v>46236</v>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E63" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
-        </is>
-      </c>
-      <c r="F63" s="15" t="inlineStr"/>
+          <t>Rideshare fares - suburban runs</t>
+        </is>
+      </c>
+      <c r="F63" s="15" t="inlineStr">
+        <is>
+          <t>Surry Hills</t>
+        </is>
+      </c>
       <c r="G63" s="16" t="n">
-        <v>29519</v>
+        <v>41221</v>
       </c>
       <c r="H63" s="16" t="n">
-        <v>29590</v>
+        <v>41402</v>
       </c>
       <c r="I63" s="16">
         <f>H63-G63</f>
@@ -4683,10 +4623,10 @@
         <v>38</v>
       </c>
       <c r="B64" s="14" t="n">
-        <v>45874</v>
+        <v>46236</v>
       </c>
       <c r="C64" s="14" t="n">
-        <v>45874</v>
+        <v>46236</v>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
@@ -4695,15 +4635,15 @@
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr"/>
       <c r="G64" s="16" t="n">
-        <v>29590</v>
+        <v>41402</v>
       </c>
       <c r="H64" s="16" t="n">
-        <v>29659</v>
+        <v>41442</v>
       </c>
       <c r="I64" s="16">
         <f>H64-G64</f>
@@ -4715,10 +4655,10 @@
         <v>39</v>
       </c>
       <c r="B65" s="14" t="n">
-        <v>45875</v>
+        <v>46237</v>
       </c>
       <c r="C65" s="14" t="n">
-        <v>45875</v>
+        <v>46237</v>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
@@ -4727,15 +4667,15 @@
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>Private use - shopping trip</t>
+          <t>Private use - personal errands</t>
         </is>
       </c>
       <c r="F65" s="15" t="inlineStr"/>
       <c r="G65" s="16" t="n">
-        <v>29659</v>
+        <v>41442</v>
       </c>
       <c r="H65" s="16" t="n">
-        <v>29702</v>
+        <v>41499</v>
       </c>
       <c r="I65" s="16">
         <f>H65-G65</f>
@@ -4747,31 +4687,27 @@
         <v>40</v>
       </c>
       <c r="B66" s="14" t="n">
-        <v>45877</v>
+        <v>46238</v>
       </c>
       <c r="C66" s="14" t="n">
-        <v>45877</v>
+        <v>46238</v>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Courier pickups and drop-offs</t>
-        </is>
-      </c>
-      <c r="F66" s="15" t="inlineStr">
-        <is>
-          <t>Kedron</t>
-        </is>
-      </c>
+          <t>Private use - shopping trip</t>
+        </is>
+      </c>
+      <c r="F66" s="15" t="inlineStr"/>
       <c r="G66" s="16" t="n">
-        <v>29702</v>
+        <v>41499</v>
       </c>
       <c r="H66" s="16" t="n">
-        <v>29833</v>
+        <v>41541</v>
       </c>
       <c r="I66" s="16">
         <f>H66-G66</f>
@@ -4783,10 +4719,10 @@
         <v>41</v>
       </c>
       <c r="B67" s="14" t="n">
-        <v>45877</v>
+        <v>46239</v>
       </c>
       <c r="C67" s="14" t="n">
-        <v>45877</v>
+        <v>46239</v>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
@@ -4795,15 +4731,15 @@
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>Private use - family travel</t>
+          <t>Private use - personal travel</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr"/>
       <c r="G67" s="16" t="n">
-        <v>29833</v>
+        <v>41541</v>
       </c>
       <c r="H67" s="16" t="n">
-        <v>29892</v>
+        <v>41605</v>
       </c>
       <c r="I67" s="16">
         <f>H67-G67</f>
@@ -4815,10 +4751,10 @@
         <v>42</v>
       </c>
       <c r="B68" s="14" t="n">
-        <v>45878</v>
+        <v>46241</v>
       </c>
       <c r="C68" s="14" t="n">
-        <v>45878</v>
+        <v>46241</v>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
@@ -4827,19 +4763,19 @@
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - evening shift</t>
+          <t>Rideshare fares - suburban runs</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>Logan Central / Fortitude Valley</t>
+          <t>Parramatta</t>
         </is>
       </c>
       <c r="G68" s="16" t="n">
-        <v>29892</v>
+        <v>41605</v>
       </c>
       <c r="H68" s="16" t="n">
-        <v>30104</v>
+        <v>41824</v>
       </c>
       <c r="I68" s="16">
         <f>H68-G68</f>
@@ -4851,31 +4787,27 @@
         <v>43</v>
       </c>
       <c r="B69" s="14" t="n">
-        <v>45879</v>
+        <v>46241</v>
       </c>
       <c r="C69" s="14" t="n">
-        <v>45879</v>
+        <v>46241</v>
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>Parcel delivery run</t>
-        </is>
-      </c>
-      <c r="F69" s="15" t="inlineStr">
-        <is>
-          <t>North Lakes</t>
-        </is>
-      </c>
+          <t>Private use - family travel</t>
+        </is>
+      </c>
+      <c r="F69" s="15" t="inlineStr"/>
       <c r="G69" s="16" t="n">
-        <v>30104</v>
+        <v>41824</v>
       </c>
       <c r="H69" s="16" t="n">
-        <v>30254</v>
+        <v>41866</v>
       </c>
       <c r="I69" s="16">
         <f>H69-G69</f>
@@ -4887,27 +4819,31 @@
         <v>44</v>
       </c>
       <c r="B70" s="14" t="n">
-        <v>45880</v>
+        <v>46242</v>
       </c>
       <c r="C70" s="14" t="n">
-        <v>45880</v>
+        <v>46242</v>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
-        </is>
-      </c>
-      <c r="F70" s="15" t="inlineStr"/>
+          <t>Rideshare fares - weekend shift</t>
+        </is>
+      </c>
+      <c r="F70" s="15" t="inlineStr">
+        <is>
+          <t>Bondi</t>
+        </is>
+      </c>
       <c r="G70" s="16" t="n">
-        <v>30254</v>
+        <v>41866</v>
       </c>
       <c r="H70" s="16" t="n">
-        <v>30322</v>
+        <v>42062</v>
       </c>
       <c r="I70" s="16">
         <f>H70-G70</f>
@@ -4919,27 +4855,31 @@
         <v>45</v>
       </c>
       <c r="B71" s="14" t="n">
-        <v>45881</v>
+        <v>46243</v>
       </c>
       <c r="C71" s="14" t="n">
-        <v>45881</v>
+        <v>46243</v>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
-        </is>
-      </c>
-      <c r="F71" s="15" t="inlineStr"/>
+          <t>Rideshare fares - event and venue pickups</t>
+        </is>
+      </c>
+      <c r="F71" s="15" t="inlineStr">
+        <is>
+          <t>Sydney Airport</t>
+        </is>
+      </c>
       <c r="G71" s="16" t="n">
-        <v>30322</v>
+        <v>42062</v>
       </c>
       <c r="H71" s="16" t="n">
-        <v>30357</v>
+        <v>42219</v>
       </c>
       <c r="I71" s="16">
         <f>H71-G71</f>
@@ -4951,10 +4891,10 @@
         <v>46</v>
       </c>
       <c r="B72" s="14" t="n">
-        <v>45882</v>
+        <v>46243</v>
       </c>
       <c r="C72" s="14" t="n">
-        <v>45882</v>
+        <v>46243</v>
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
@@ -4963,15 +4903,15 @@
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Private use - shopping trip</t>
+          <t>Private use - personal errands</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr"/>
       <c r="G72" s="16" t="n">
-        <v>30357</v>
+        <v>42219</v>
       </c>
       <c r="H72" s="16" t="n">
-        <v>30429</v>
+        <v>42253</v>
       </c>
       <c r="I72" s="16">
         <f>H72-G72</f>
@@ -4983,10 +4923,10 @@
         <v>47</v>
       </c>
       <c r="B73" s="14" t="n">
-        <v>45883</v>
+        <v>46244</v>
       </c>
       <c r="C73" s="14" t="n">
-        <v>45883</v>
+        <v>46244</v>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
@@ -4995,15 +4935,15 @@
       </c>
       <c r="E73" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
+          <t>Private use - family travel</t>
         </is>
       </c>
       <c r="F73" s="15" t="inlineStr"/>
       <c r="G73" s="16" t="n">
-        <v>30429</v>
+        <v>42253</v>
       </c>
       <c r="H73" s="16" t="n">
-        <v>30500</v>
+        <v>42283</v>
       </c>
       <c r="I73" s="16">
         <f>H73-G73</f>
@@ -5015,31 +4955,27 @@
         <v>48</v>
       </c>
       <c r="B74" s="14" t="n">
-        <v>45884</v>
+        <v>46246</v>
       </c>
       <c r="C74" s="14" t="n">
-        <v>45884</v>
+        <v>46246</v>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - suburban runs</t>
-        </is>
-      </c>
-      <c r="F74" s="15" t="inlineStr">
-        <is>
-          <t>West End / Fortitude Valley</t>
-        </is>
-      </c>
+          <t>Private use - personal errands</t>
+        </is>
+      </c>
+      <c r="F74" s="15" t="inlineStr"/>
       <c r="G74" s="16" t="n">
-        <v>30500</v>
+        <v>42283</v>
       </c>
       <c r="H74" s="16" t="n">
-        <v>30708</v>
+        <v>42357</v>
       </c>
       <c r="I74" s="16">
         <f>H74-G74</f>
@@ -5051,10 +4987,10 @@
         <v>49</v>
       </c>
       <c r="B75" s="14" t="n">
-        <v>45884</v>
+        <v>46247</v>
       </c>
       <c r="C75" s="14" t="n">
-        <v>45884</v>
+        <v>46247</v>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
@@ -5063,15 +4999,15 @@
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
+          <t>Private use - family travel</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr"/>
       <c r="G75" s="16" t="n">
-        <v>30708</v>
+        <v>42357</v>
       </c>
       <c r="H75" s="16" t="n">
-        <v>30764</v>
+        <v>42413</v>
       </c>
       <c r="I75" s="16">
         <f>H75-G75</f>
@@ -5083,10 +5019,10 @@
         <v>50</v>
       </c>
       <c r="B76" s="14" t="n">
-        <v>45885</v>
+        <v>46248</v>
       </c>
       <c r="C76" s="14" t="n">
-        <v>45885</v>
+        <v>46248</v>
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
@@ -5095,19 +5031,19 @@
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Late night delivery run</t>
+          <t>Rideshare fares - weekend shift</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>Everton Park / Mount Gravatt</t>
+          <t>Surry Hills</t>
         </is>
       </c>
       <c r="G76" s="16" t="n">
-        <v>30764</v>
+        <v>42413</v>
       </c>
       <c r="H76" s="16" t="n">
-        <v>30958</v>
+        <v>42624</v>
       </c>
       <c r="I76" s="16">
         <f>H76-G76</f>
@@ -5119,27 +5055,31 @@
         <v>51</v>
       </c>
       <c r="B77" s="14" t="n">
-        <v>45885</v>
+        <v>46249</v>
       </c>
       <c r="C77" s="14" t="n">
-        <v>45885</v>
+        <v>46249</v>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
-        </is>
-      </c>
-      <c r="F77" s="15" t="inlineStr"/>
+          <t>Rideshare fares - passenger trips</t>
+        </is>
+      </c>
+      <c r="F77" s="15" t="inlineStr">
+        <is>
+          <t>Sydney CBD / Castle Hill</t>
+        </is>
+      </c>
       <c r="G77" s="16" t="n">
-        <v>30958</v>
+        <v>42624</v>
       </c>
       <c r="H77" s="16" t="n">
-        <v>30988</v>
+        <v>42906</v>
       </c>
       <c r="I77" s="16">
         <f>H77-G77</f>
@@ -5151,10 +5091,10 @@
         <v>52</v>
       </c>
       <c r="B78" s="14" t="n">
-        <v>45886</v>
+        <v>46250</v>
       </c>
       <c r="C78" s="14" t="n">
-        <v>45886</v>
+        <v>46250</v>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
@@ -5163,19 +5103,19 @@
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Parcel delivery run</t>
+          <t>Rideshare fares - late night runs</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>Newstead</t>
+          <t>Sydney Airport</t>
         </is>
       </c>
       <c r="G78" s="16" t="n">
-        <v>30988</v>
+        <v>42906</v>
       </c>
       <c r="H78" s="16" t="n">
-        <v>31070</v>
+        <v>43140</v>
       </c>
       <c r="I78" s="16">
         <f>H78-G78</f>
@@ -5187,10 +5127,10 @@
         <v>53</v>
       </c>
       <c r="B79" s="14" t="n">
-        <v>45886</v>
+        <v>46254</v>
       </c>
       <c r="C79" s="14" t="n">
-        <v>45886</v>
+        <v>46254</v>
       </c>
       <c r="D79" s="13" t="inlineStr">
         <is>
@@ -5199,15 +5139,15 @@
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
+          <t>Private use - weekend outing</t>
         </is>
       </c>
       <c r="F79" s="15" t="inlineStr"/>
       <c r="G79" s="16" t="n">
-        <v>31070</v>
+        <v>43140</v>
       </c>
       <c r="H79" s="16" t="n">
-        <v>31112</v>
+        <v>43204</v>
       </c>
       <c r="I79" s="16">
         <f>H79-G79</f>
@@ -5219,27 +5159,31 @@
         <v>54</v>
       </c>
       <c r="B80" s="14" t="n">
-        <v>45887</v>
+        <v>46255</v>
       </c>
       <c r="C80" s="14" t="n">
-        <v>45887</v>
+        <v>46255</v>
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
-        </is>
-      </c>
-      <c r="F80" s="15" t="inlineStr"/>
+          <t>Rideshare fares - passenger trips</t>
+        </is>
+      </c>
+      <c r="F80" s="15" t="inlineStr">
+        <is>
+          <t>Surry Hills</t>
+        </is>
+      </c>
       <c r="G80" s="16" t="n">
-        <v>31112</v>
+        <v>43204</v>
       </c>
       <c r="H80" s="16" t="n">
-        <v>31152</v>
+        <v>43336</v>
       </c>
       <c r="I80" s="16">
         <f>H80-G80</f>
@@ -5251,27 +5195,31 @@
         <v>55</v>
       </c>
       <c r="B81" s="14" t="n">
-        <v>45889</v>
+        <v>46256</v>
       </c>
       <c r="C81" s="14" t="n">
-        <v>45889</v>
+        <v>46256</v>
       </c>
       <c r="D81" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
-        </is>
-      </c>
-      <c r="F81" s="15" t="inlineStr"/>
+          <t>Rideshare fares - late night runs</t>
+        </is>
+      </c>
+      <c r="F81" s="15" t="inlineStr">
+        <is>
+          <t>Sydney CBD / Randwick</t>
+        </is>
+      </c>
       <c r="G81" s="16" t="n">
-        <v>31152</v>
+        <v>43336</v>
       </c>
       <c r="H81" s="16" t="n">
-        <v>31221</v>
+        <v>43608</v>
       </c>
       <c r="I81" s="16">
         <f>H81-G81</f>
@@ -5283,31 +5231,27 @@
         <v>56</v>
       </c>
       <c r="B82" s="14" t="n">
-        <v>45891</v>
+        <v>46256</v>
       </c>
       <c r="C82" s="14" t="n">
-        <v>45891</v>
+        <v>46256</v>
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - suburban runs</t>
-        </is>
-      </c>
-      <c r="F82" s="15" t="inlineStr">
-        <is>
-          <t>Brisbane CBD</t>
-        </is>
-      </c>
+          <t>Private use - personal travel</t>
+        </is>
+      </c>
+      <c r="F82" s="15" t="inlineStr"/>
       <c r="G82" s="16" t="n">
-        <v>31221</v>
+        <v>43608</v>
       </c>
       <c r="H82" s="16" t="n">
-        <v>31397</v>
+        <v>43675</v>
       </c>
       <c r="I82" s="16">
         <f>H82-G82</f>
@@ -5319,10 +5263,10 @@
         <v>57</v>
       </c>
       <c r="B83" s="14" t="n">
-        <v>45891</v>
+        <v>46259</v>
       </c>
       <c r="C83" s="14" t="n">
-        <v>45891</v>
+        <v>46259</v>
       </c>
       <c r="D83" s="13" t="inlineStr">
         <is>
@@ -5331,15 +5275,15 @@
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
+          <t>Private use - visiting friends</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr"/>
       <c r="G83" s="16" t="n">
-        <v>31397</v>
+        <v>43675</v>
       </c>
       <c r="H83" s="16" t="n">
-        <v>31428</v>
+        <v>43740</v>
       </c>
       <c r="I83" s="16">
         <f>H83-G83</f>
@@ -5351,31 +5295,27 @@
         <v>58</v>
       </c>
       <c r="B84" s="14" t="n">
-        <v>45892</v>
+        <v>46260</v>
       </c>
       <c r="C84" s="14" t="n">
-        <v>45892</v>
+        <v>46260</v>
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Courier pickups and drop-offs</t>
-        </is>
-      </c>
-      <c r="F84" s="15" t="inlineStr">
-        <is>
-          <t>Chermside</t>
-        </is>
-      </c>
+          <t>Private use - shopping trip</t>
+        </is>
+      </c>
+      <c r="F84" s="15" t="inlineStr"/>
       <c r="G84" s="16" t="n">
-        <v>31428</v>
+        <v>43740</v>
       </c>
       <c r="H84" s="16" t="n">
-        <v>31598</v>
+        <v>43802</v>
       </c>
       <c r="I84" s="16">
         <f>H84-G84</f>
@@ -5387,31 +5327,27 @@
         <v>59</v>
       </c>
       <c r="B85" s="14" t="n">
-        <v>45893</v>
+        <v>46261</v>
       </c>
       <c r="C85" s="14" t="n">
-        <v>45893</v>
+        <v>46261</v>
       </c>
       <c r="D85" s="13" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Private</t>
         </is>
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>Rideshare fares - suburban runs</t>
-        </is>
-      </c>
-      <c r="F85" s="15" t="inlineStr">
-        <is>
-          <t>Chermside</t>
-        </is>
-      </c>
+          <t>Private use - shopping trip</t>
+        </is>
+      </c>
+      <c r="F85" s="15" t="inlineStr"/>
       <c r="G85" s="16" t="n">
-        <v>31598</v>
+        <v>43802</v>
       </c>
       <c r="H85" s="16" t="n">
-        <v>31749</v>
+        <v>43849</v>
       </c>
       <c r="I85" s="16">
         <f>H85-G85</f>
@@ -5423,10 +5359,10 @@
         <v>60</v>
       </c>
       <c r="B86" s="14" t="n">
-        <v>45894</v>
+        <v>46262</v>
       </c>
       <c r="C86" s="14" t="n">
-        <v>45894</v>
+        <v>46262</v>
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
@@ -5435,15 +5371,15 @@
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t>Private use - personal errands</t>
+          <t>Private use - shopping trip</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr"/>
       <c r="G86" s="16" t="n">
-        <v>31749</v>
+        <v>43849</v>
       </c>
       <c r="H86" s="16" t="n">
-        <v>31801</v>
+        <v>43883</v>
       </c>
       <c r="I86" s="16">
         <f>H86-G86</f>
@@ -5455,27 +5391,31 @@
         <v>61</v>
       </c>
       <c r="B87" s="14" t="n">
-        <v>45895</v>
+        <v>46263</v>
       </c>
       <c r="C87" s="14" t="n">
-        <v>45895</v>
+        <v>46263</v>
       </c>
       <c r="D87" s="13" t="inlineStr">
         <is>
-          <t>Private</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="E87" s="15" t="inlineStr">
         <is>
-          <t>Private use - visiting friends</t>
-        </is>
-      </c>
-      <c r="F87" s="15" t="inlineStr"/>
+          <t>Rideshare fares - morning peak</t>
+        </is>
+      </c>
+      <c r="F87" s="15" t="inlineStr">
+        <is>
+          <t>Pyrmont</t>
+        </is>
+      </c>
       <c r="G87" s="16" t="n">
-        <v>31801</v>
+        <v>43883</v>
       </c>
       <c r="H87" s="16" t="n">
-        <v>31845</v>
+        <v>44130</v>
       </c>
       <c r="I87" s="16">
         <f>H87-G87</f>
@@ -5487,10 +5427,10 @@
         <v>62</v>
       </c>
       <c r="B88" s="14" t="n">
-        <v>45899</v>
+        <v>46263</v>
       </c>
       <c r="C88" s="14" t="n">
-        <v>45899</v>
+        <v>46263</v>
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
@@ -5499,15 +5439,15 @@
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Private use - weekend outing</t>
+          <t>Private use - visiting friends</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr"/>
       <c r="G88" s="16" t="n">
-        <v>31845</v>
+        <v>44130</v>
       </c>
       <c r="H88" s="16" t="n">
-        <v>31884</v>
+        <v>44176</v>
       </c>
       <c r="I88" s="16">
         <f>H88-G88</f>
@@ -5519,10 +5459,10 @@
         <v>63</v>
       </c>
       <c r="B89" s="14" t="n">
-        <v>45900</v>
+        <v>46264</v>
       </c>
       <c r="C89" s="14" t="n">
-        <v>45900</v>
+        <v>46264</v>
       </c>
       <c r="D89" s="13" t="inlineStr">
         <is>
@@ -5531,19 +5471,19 @@
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>Parcel delivery run</t>
+          <t>Rideshare fares - weekend shift</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
         <is>
-          <t>Mount Gravatt</t>
+          <t>Bondi</t>
         </is>
       </c>
       <c r="G89" s="16" t="n">
-        <v>31884</v>
+        <v>44176</v>
       </c>
       <c r="H89" s="16" t="n">
-        <v>32000</v>
+        <v>44426</v>
       </c>
       <c r="I89" s="16">
         <f>H89-G89</f>
@@ -5551,186 +5491,782 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="17" t="inlineStr">
+      <c r="A90" s="13" t="n">
+        <v>64</v>
+      </c>
+      <c r="B90" s="14" t="n">
+        <v>46264</v>
+      </c>
+      <c r="C90" s="14" t="n">
+        <v>46264</v>
+      </c>
+      <c r="D90" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>Private use - weekend outing</t>
+        </is>
+      </c>
+      <c r="F90" s="15" t="inlineStr"/>
+      <c r="G90" s="16" t="n">
+        <v>44426</v>
+      </c>
+      <c r="H90" s="16" t="n">
+        <v>44459</v>
+      </c>
+      <c r="I90" s="16">
+        <f>H90-G90</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="n">
+        <v>65</v>
+      </c>
+      <c r="B91" s="14" t="n">
+        <v>46266</v>
+      </c>
+      <c r="C91" s="14" t="n">
+        <v>46266</v>
+      </c>
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E91" s="15" t="inlineStr">
+        <is>
+          <t>Private use - family travel</t>
+        </is>
+      </c>
+      <c r="F91" s="15" t="inlineStr"/>
+      <c r="G91" s="16" t="n">
+        <v>44459</v>
+      </c>
+      <c r="H91" s="16" t="n">
+        <v>44492</v>
+      </c>
+      <c r="I91" s="16">
+        <f>H91-G91</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="n">
+        <v>66</v>
+      </c>
+      <c r="B92" s="14" t="n">
+        <v>46267</v>
+      </c>
+      <c r="C92" s="14" t="n">
+        <v>46267</v>
+      </c>
+      <c r="D92" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>Private use - family travel</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="inlineStr"/>
+      <c r="G92" s="16" t="n">
+        <v>44492</v>
+      </c>
+      <c r="H92" s="16" t="n">
+        <v>44554</v>
+      </c>
+      <c r="I92" s="16">
+        <f>H92-G92</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="n">
+        <v>67</v>
+      </c>
+      <c r="B93" s="14" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C93" s="14" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D93" s="13" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>Rideshare fares - evening shift</t>
+        </is>
+      </c>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>Newtown / Surry Hills</t>
+        </is>
+      </c>
+      <c r="G93" s="16" t="n">
+        <v>44554</v>
+      </c>
+      <c r="H93" s="16" t="n">
+        <v>44904</v>
+      </c>
+      <c r="I93" s="16">
+        <f>H93-G93</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="n">
+        <v>68</v>
+      </c>
+      <c r="B94" s="14" t="n">
+        <v>46269</v>
+      </c>
+      <c r="C94" s="14" t="n">
+        <v>46269</v>
+      </c>
+      <c r="D94" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>Private use - family travel</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr"/>
+      <c r="G94" s="16" t="n">
+        <v>44904</v>
+      </c>
+      <c r="H94" s="16" t="n">
+        <v>44929</v>
+      </c>
+      <c r="I94" s="16">
+        <f>H94-G94</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="n">
+        <v>69</v>
+      </c>
+      <c r="B95" s="14" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C95" s="14" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D95" s="13" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>Rideshare fares - airport transfers</t>
+        </is>
+      </c>
+      <c r="F95" s="15" t="inlineStr">
+        <is>
+          <t>Surry Hills / Sydney CBD</t>
+        </is>
+      </c>
+      <c r="G95" s="16" t="n">
+        <v>44929</v>
+      </c>
+      <c r="H95" s="16" t="n">
+        <v>45266</v>
+      </c>
+      <c r="I95" s="16">
+        <f>H95-G95</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="n">
+        <v>70</v>
+      </c>
+      <c r="B96" s="14" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C96" s="14" t="n">
+        <v>46270</v>
+      </c>
+      <c r="D96" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>Private use - visiting friends</t>
+        </is>
+      </c>
+      <c r="F96" s="15" t="inlineStr"/>
+      <c r="G96" s="16" t="n">
+        <v>45266</v>
+      </c>
+      <c r="H96" s="16" t="n">
+        <v>45308</v>
+      </c>
+      <c r="I96" s="16">
+        <f>H96-G96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="B97" s="14" t="n">
+        <v>46271</v>
+      </c>
+      <c r="C97" s="14" t="n">
+        <v>46271</v>
+      </c>
+      <c r="D97" s="13" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>Rideshare fares - late night runs</t>
+        </is>
+      </c>
+      <c r="F97" s="15" t="inlineStr">
+        <is>
+          <t>Marrickville / Sydney Airport</t>
+        </is>
+      </c>
+      <c r="G97" s="16" t="n">
+        <v>45308</v>
+      </c>
+      <c r="H97" s="16" t="n">
+        <v>45591</v>
+      </c>
+      <c r="I97" s="16">
+        <f>H97-G97</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="n">
+        <v>72</v>
+      </c>
+      <c r="B98" s="14" t="n">
+        <v>46273</v>
+      </c>
+      <c r="C98" s="14" t="n">
+        <v>46273</v>
+      </c>
+      <c r="D98" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>Private use - personal travel</t>
+        </is>
+      </c>
+      <c r="F98" s="15" t="inlineStr"/>
+      <c r="G98" s="16" t="n">
+        <v>45591</v>
+      </c>
+      <c r="H98" s="16" t="n">
+        <v>45637</v>
+      </c>
+      <c r="I98" s="16">
+        <f>H98-G98</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="n">
+        <v>73</v>
+      </c>
+      <c r="B99" s="14" t="n">
+        <v>46274</v>
+      </c>
+      <c r="C99" s="14" t="n">
+        <v>46274</v>
+      </c>
+      <c r="D99" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>Private use - visiting friends</t>
+        </is>
+      </c>
+      <c r="F99" s="15" t="inlineStr"/>
+      <c r="G99" s="16" t="n">
+        <v>45637</v>
+      </c>
+      <c r="H99" s="16" t="n">
+        <v>45682</v>
+      </c>
+      <c r="I99" s="16">
+        <f>H99-G99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="n">
+        <v>74</v>
+      </c>
+      <c r="B100" s="14" t="n">
+        <v>46275</v>
+      </c>
+      <c r="C100" s="14" t="n">
+        <v>46275</v>
+      </c>
+      <c r="D100" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>Private use - weekend outing</t>
+        </is>
+      </c>
+      <c r="F100" s="15" t="inlineStr"/>
+      <c r="G100" s="16" t="n">
+        <v>45682</v>
+      </c>
+      <c r="H100" s="16" t="n">
+        <v>45753</v>
+      </c>
+      <c r="I100" s="16">
+        <f>H100-G100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="B101" s="14" t="n">
+        <v>46276</v>
+      </c>
+      <c r="C101" s="14" t="n">
+        <v>46276</v>
+      </c>
+      <c r="D101" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>Private use - weekend outing</t>
+        </is>
+      </c>
+      <c r="F101" s="15" t="inlineStr"/>
+      <c r="G101" s="16" t="n">
+        <v>45753</v>
+      </c>
+      <c r="H101" s="16" t="n">
+        <v>45810</v>
+      </c>
+      <c r="I101" s="16">
+        <f>H101-G101</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="n">
+        <v>76</v>
+      </c>
+      <c r="B102" s="14" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C102" s="14" t="n">
+        <v>46277</v>
+      </c>
+      <c r="D102" s="13" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>Rideshare fares - morning peak</t>
+        </is>
+      </c>
+      <c r="F102" s="15" t="inlineStr">
+        <is>
+          <t>Bondi</t>
+        </is>
+      </c>
+      <c r="G102" s="16" t="n">
+        <v>45810</v>
+      </c>
+      <c r="H102" s="16" t="n">
+        <v>46006</v>
+      </c>
+      <c r="I102" s="16">
+        <f>H102-G102</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="B103" s="14" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C103" s="14" t="n">
+        <v>46277</v>
+      </c>
+      <c r="D103" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E103" s="15" t="inlineStr">
+        <is>
+          <t>Private use - weekend outing</t>
+        </is>
+      </c>
+      <c r="F103" s="15" t="inlineStr"/>
+      <c r="G103" s="16" t="n">
+        <v>46006</v>
+      </c>
+      <c r="H103" s="16" t="n">
+        <v>46039</v>
+      </c>
+      <c r="I103" s="16">
+        <f>H103-G103</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="n">
+        <v>78</v>
+      </c>
+      <c r="B104" s="14" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C104" s="14" t="n">
+        <v>46278</v>
+      </c>
+      <c r="D104" s="13" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>Rideshare fares - passenger trips</t>
+        </is>
+      </c>
+      <c r="F104" s="15" t="inlineStr">
+        <is>
+          <t>Parramatta / Surry Hills</t>
+        </is>
+      </c>
+      <c r="G104" s="16" t="n">
+        <v>46039</v>
+      </c>
+      <c r="H104" s="16" t="n">
+        <v>46347</v>
+      </c>
+      <c r="I104" s="16">
+        <f>H104-G104</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="B105" s="14" t="n">
+        <v>46280</v>
+      </c>
+      <c r="C105" s="14" t="n">
+        <v>46280</v>
+      </c>
+      <c r="D105" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E105" s="15" t="inlineStr">
+        <is>
+          <t>Private use - family travel</t>
+        </is>
+      </c>
+      <c r="F105" s="15" t="inlineStr"/>
+      <c r="G105" s="16" t="n">
+        <v>46347</v>
+      </c>
+      <c r="H105" s="16" t="n">
+        <v>46411</v>
+      </c>
+      <c r="I105" s="16">
+        <f>H105-G105</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="n">
+        <v>80</v>
+      </c>
+      <c r="B106" s="14" t="n">
+        <v>46281</v>
+      </c>
+      <c r="C106" s="14" t="n">
+        <v>46281</v>
+      </c>
+      <c r="D106" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="inlineStr">
+        <is>
+          <t>Private use - visiting friends</t>
+        </is>
+      </c>
+      <c r="F106" s="15" t="inlineStr"/>
+      <c r="G106" s="16" t="n">
+        <v>46411</v>
+      </c>
+      <c r="H106" s="16" t="n">
+        <v>46455</v>
+      </c>
+      <c r="I106" s="16">
+        <f>H106-G106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="n">
+        <v>81</v>
+      </c>
+      <c r="B107" s="14" t="n">
+        <v>46282</v>
+      </c>
+      <c r="C107" s="14" t="n">
+        <v>46282</v>
+      </c>
+      <c r="D107" s="13" t="inlineStr">
+        <is>
+          <t>Private</t>
+        </is>
+      </c>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>Private use - personal errands</t>
+        </is>
+      </c>
+      <c r="F107" s="15" t="inlineStr"/>
+      <c r="G107" s="16" t="n">
+        <v>46455</v>
+      </c>
+      <c r="H107" s="16" t="n">
+        <v>46500</v>
+      </c>
+      <c r="I107" s="16">
+        <f>H107-G107</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="17" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B90" s="15" t="n"/>
-      <c r="C90" s="15" t="n"/>
-      <c r="D90" s="15" t="n"/>
-      <c r="E90" s="15" t="n"/>
-      <c r="F90" s="18" t="inlineStr">
+      <c r="B108" s="15" t="n"/>
+      <c r="C108" s="15" t="n"/>
+      <c r="D108" s="15" t="n"/>
+      <c r="E108" s="15" t="n"/>
+      <c r="F108" s="18" t="inlineStr">
         <is>
           <t>Total kilometres</t>
         </is>
       </c>
-      <c r="G90" s="15" t="n"/>
-      <c r="H90" s="15" t="n"/>
-      <c r="I90" s="19">
-        <f>SUM(I27:I89)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91">
-      <c r="F91" s="18" t="inlineStr">
+      <c r="G108" s="15" t="n"/>
+      <c r="H108" s="15" t="n"/>
+      <c r="I108" s="19">
+        <f>SUM(I27:I107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="F109" s="18" t="inlineStr">
         <is>
           <t>Business kilometres</t>
         </is>
       </c>
-      <c r="I91" s="19">
-        <f>SUMIF($D$27:$D$89,"Business",$I$27:$I$89)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92">
-      <c r="F92" s="18" t="inlineStr">
+      <c r="I109" s="19">
+        <f>SUMIF($D$27:$D$107,"Business",$I$27:$I$107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="F110" s="18" t="inlineStr">
         <is>
           <t>Private kilometres</t>
         </is>
       </c>
-      <c r="I92" s="19">
-        <f>SUMIF($D$27:$D$89,"Private",$I$27:$I$89)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93">
-      <c r="F93" s="18" t="inlineStr">
+      <c r="I110" s="19">
+        <f>SUMIF($D$27:$D$107,"Private",$I$27:$I$107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="F111" s="18" t="inlineStr">
         <is>
           <t>Business-use percentage</t>
         </is>
       </c>
-      <c r="I93" s="20">
-        <f>IFERROR(I91/I90,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="I111" s="20">
+        <f>IFERROR(I109/I108,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>Odometer readings for each income year</t>
         </is>
       </c>
-      <c r="B96" s="4" t="n"/>
-      <c r="C96" s="4" t="n"/>
-      <c r="D96" s="4" t="n"/>
-      <c r="E96" s="4" t="n"/>
-      <c r="F96" s="4" t="n"/>
-      <c r="G96" s="4" t="n"/>
-      <c r="H96" s="4" t="n"/>
-      <c r="I96" s="4" t="n"/>
-    </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="B97" s="12" t="inlineStr">
+      <c r="B114" s="4" t="n"/>
+      <c r="C114" s="4" t="n"/>
+      <c r="D114" s="4" t="n"/>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="n"/>
+      <c r="G114" s="4" t="n"/>
+      <c r="H114" s="4" t="n"/>
+      <c r="I114" s="4" t="n"/>
+    </row>
+    <row r="115" ht="30" customHeight="1">
+      <c r="B115" s="12" t="inlineStr">
         <is>
           <t>Income year</t>
         </is>
       </c>
-      <c r="C97" s="12" t="inlineStr">
+      <c r="C115" s="12" t="inlineStr">
         <is>
           <t>Odometer at start of year</t>
         </is>
       </c>
-      <c r="D97" s="12" t="inlineStr">
+      <c r="D115" s="12" t="inlineStr">
         <is>
           <t>Odometer at end of year</t>
         </is>
       </c>
-      <c r="E97" s="12" t="inlineStr">
+      <c r="E115" s="12" t="inlineStr">
         <is>
           <t>Total km for the year</t>
         </is>
       </c>
-      <c r="F97" s="12" t="inlineStr">
+      <c r="F115" s="12" t="inlineStr">
         <is>
           <t>Business km at the logbook percentage</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="B98" s="13" t="inlineStr">
-        <is>
-          <t>2025-26</t>
-        </is>
-      </c>
-      <c r="C98" s="16" t="n">
-        <v>25954</v>
-      </c>
-      <c r="D98" s="16" t="n"/>
-      <c r="E98" s="16">
-        <f>IF(COUNT(C98:D98)=2,D98-C98,"")</f>
-        <v/>
-      </c>
-      <c r="F98" s="16">
-        <f>IF(ISNUMBER(E98),ROUND(E98*$D$23,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99">
-      <c r="B99" s="13" t="inlineStr">
+    <row r="116">
+      <c r="B116" s="13" t="inlineStr">
         <is>
           <t>2026-27</t>
         </is>
       </c>
-      <c r="C99" s="16" t="n"/>
-      <c r="D99" s="16" t="n"/>
-      <c r="E99" s="16">
-        <f>IF(COUNT(C99:D99)=2,D99-C99,"")</f>
-        <v/>
-      </c>
-      <c r="F99" s="16">
-        <f>IF(ISNUMBER(E99),ROUND(E99*$D$23,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="B100" s="13" t="inlineStr">
+      <c r="C116" s="16" t="n">
+        <v>37185</v>
+      </c>
+      <c r="D116" s="16" t="n"/>
+      <c r="E116" s="16">
+        <f>IF(COUNT(C116:D116)=2,D116-C116,"")</f>
+        <v/>
+      </c>
+      <c r="F116" s="16">
+        <f>IF(ISNUMBER(E116),ROUND(E116*$D$23,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="13" t="inlineStr">
         <is>
           <t>2027-28</t>
         </is>
       </c>
-      <c r="C100" s="16" t="n"/>
-      <c r="D100" s="16" t="n"/>
-      <c r="E100" s="16">
-        <f>IF(COUNT(C100:D100)=2,D100-C100,"")</f>
-        <v/>
-      </c>
-      <c r="F100" s="16">
-        <f>IF(ISNUMBER(E100),ROUND(E100*$D$23,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101">
-      <c r="B101" s="13" t="inlineStr">
+      <c r="C117" s="16" t="n"/>
+      <c r="D117" s="16" t="n"/>
+      <c r="E117" s="16">
+        <f>IF(COUNT(C117:D117)=2,D117-C117,"")</f>
+        <v/>
+      </c>
+      <c r="F117" s="16">
+        <f>IF(ISNUMBER(E117),ROUND(E117*$D$23,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="13" t="inlineStr">
         <is>
           <t>2028-29</t>
         </is>
       </c>
-      <c r="C101" s="16" t="n"/>
-      <c r="D101" s="16" t="n"/>
-      <c r="E101" s="16">
-        <f>IF(COUNT(C101:D101)=2,D101-C101,"")</f>
-        <v/>
-      </c>
-      <c r="F101" s="16">
-        <f>IF(ISNUMBER(E101),ROUND(E101*$D$23,0),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="B102" s="13" t="inlineStr">
+      <c r="C118" s="16" t="n"/>
+      <c r="D118" s="16" t="n"/>
+      <c r="E118" s="16">
+        <f>IF(COUNT(C118:D118)=2,D118-C118,"")</f>
+        <v/>
+      </c>
+      <c r="F118" s="16">
+        <f>IF(ISNUMBER(E118),ROUND(E118*$D$23,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="13" t="inlineStr">
         <is>
           <t>2029-30</t>
         </is>
       </c>
-      <c r="C102" s="16" t="n"/>
-      <c r="D102" s="16" t="n"/>
-      <c r="E102" s="16">
-        <f>IF(COUNT(C102:D102)=2,D102-C102,"")</f>
-        <v/>
-      </c>
-      <c r="F102" s="16">
-        <f>IF(ISNUMBER(E102),ROUND(E102*$D$23,0),"")</f>
+      <c r="C119" s="16" t="n"/>
+      <c r="D119" s="16" t="n"/>
+      <c r="E119" s="16">
+        <f>IF(COUNT(C119:D119)=2,D119-C119,"")</f>
+        <v/>
+      </c>
+      <c r="F119" s="16">
+        <f>IF(ISNUMBER(E119),ROUND(E119*$D$23,0),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>2030-31</t>
+        </is>
+      </c>
+      <c r="C120" s="16" t="n"/>
+      <c r="D120" s="16" t="n"/>
+      <c r="E120" s="16">
+        <f>IF(COUNT(C120:D120)=2,D120-C120,"")</f>
+        <v/>
+      </c>
+      <c r="F120" s="16">
+        <f>IF(ISNUMBER(E120),ROUND(E120*$D$23,0),"")</f>
         <v/>
       </c>
     </row>
@@ -5753,7 +6289,6 @@
     <mergeCell ref="A4:I4"/>
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D8:I8"/>
-    <mergeCell ref="A96:I96"/>
     <mergeCell ref="D15:I15"/>
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="D24:I24"/>
@@ -5765,6 +6300,7 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="D20:I20"/>
     <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A114:I114"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="D10:I10"/>
     <mergeCell ref="D22:I22"/>
